--- a/output/auditoria_dashboard.xlsx
+++ b/output/auditoria_dashboard.xlsx
@@ -485,7 +485,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-05-25 18:43</t>
+          <t>2026-05-26 09:22</t>
         </is>
       </c>
     </row>
@@ -20424,10 +20424,10 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>650.04</v>
+        <v>1211.4</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>650.04</v>
+        <v>1211.4</v>
       </c>
       <c r="E49" s="4" t="n">
         <v>0</v>

--- a/output/auditoria_dashboard.xlsx
+++ b/output/auditoria_dashboard.xlsx
@@ -485,7 +485,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-05-26 09:22</t>
+          <t>2026-05-26 10:31</t>
         </is>
       </c>
     </row>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Ningún cambio respecto al baseline del 2026-05-25.</t>
+          <t>Ningún cambio respecto al baseline del 2026-05-26.</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr"/>
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Ningún cambio respecto al baseline del 2026-05-25.</t>
+          <t>Ningún cambio respecto al baseline del 2026-05-26.</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr"/>

--- a/output/auditoria_dashboard.xlsx
+++ b/output/auditoria_dashboard.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K190"/>
+  <dimension ref="A1:K187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -474,7 +474,7 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="59" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -485,7 +485,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-05-26 10:31</t>
+          <t>2026-06-18 15:24</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0 criticos / 37 avisos / 148 OK</t>
+          <t>0 criticos / 38 avisos / 144 OK</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Duplicados</t>
+          <t>Distorsion_CrossMonth</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -771,26 +771,32 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Guest×mes 2024-07: Lucy Rankin</t>
+          <t>CrossMonth 2027-06: Pablo Ruiz</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>code='' 2n 270.0€ bd=2024-03-01 | code='' 6n 723.0€ bd=2024-01-29</t>
+          <t>6n en 06/2027 + 3n en 07/2027  Total reserva=1047€  Distorsión=329€ (11% del mes)  33% de las noches son del mes siguiente</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2024</v>
+        <v>2027</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
-      <c r="J10" s="3" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>2643.19</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>2972.05</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Mismo huésped, mismo mes, múltiples ingresos</t>
+          <t>Sin distorsión, 06/2027 mostraría ~2643€ en lugar de 2972€. Los 3n restantes están en 07/2027.</t>
         </is>
       </c>
     </row>
@@ -812,26 +818,26 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Registro sin código ni checkin con ingreso 2024-01</t>
+          <t>Guest×mes 2024-07: Lucy Rankin</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Maitane Renart code='' checkin='' total=208.0€ nights=3 — posible duplicado</t>
+          <t>code='' 2n 270.0€ bd=2024-03-01 | code='' 6n 723.0€ bd=2024-01-29</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
         <v>2024</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Registro sin code ni checkin pero con ingreso — verificar</t>
+          <t>Mismo huésped, mismo mes, múltiples ingresos</t>
         </is>
       </c>
     </row>
@@ -853,19 +859,19 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Registro sin código ni checkin con ingreso 2024-07</t>
+          <t>Registro sin código ni checkin con ingreso 2024-01</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Lucy Rankin code='' checkin='' total=270.0€ nights=2 — posible duplicado</t>
+          <t>Maitane Renart code='' checkin='' total=208.0€ nights=3 — posible duplicado</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
         <v>2024</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H12" s="3" t="inlineStr"/>
       <c r="I12" s="3" t="inlineStr"/>
@@ -894,19 +900,19 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Registro sin código ni checkin con ingreso 2024-11</t>
+          <t>Registro sin código ni checkin con ingreso 2024-07</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Fabio Mora code='' checkin='' total=222.29€ nights=4 — posible duplicado</t>
+          <t>Lucy Rankin code='' checkin='' total=270.0€ nights=2 — posible duplicado</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
         <v>2024</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H13" s="3" t="inlineStr"/>
       <c r="I13" s="3" t="inlineStr"/>
@@ -935,19 +941,19 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Registro sin código ni checkin con ingreso 2025-01</t>
+          <t>Registro sin código ni checkin con ingreso 2024-11</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Isabel Jung code='' checkin='' total=185.0€ nights=3 — posible duplicado</t>
+          <t>Fabio Mora code='' checkin='' total=222.29€ nights=4 — posible duplicado</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H14" s="3" t="inlineStr"/>
       <c r="I14" s="3" t="inlineStr"/>
@@ -976,19 +982,19 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Registro sin código ni checkin con ingreso 2025-08</t>
+          <t>Registro sin código ni checkin con ingreso 2025-01</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Marta Berdejo code='' checkin='' total=139.0€ nights=1 — posible duplicado</t>
+          <t>Isabel Jung code='' checkin='' total=185.0€ nights=3 — posible duplicado</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
         <v>2025</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
       <c r="I15" s="3" t="inlineStr"/>
@@ -1002,7 +1008,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Solapes</t>
+          <t>Duplicados</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1017,16 +1023,16 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Solape historico</t>
+          <t>Registro sin código ni checkin con ingreso 2025-08</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>12 Ashley 2016-08-01-&gt;2016-08-04  &lt;-&gt;  13 Eva 2016-08-03-&gt;2016-08-07</t>
+          <t>Marta Berdejo code='' checkin='' total=139.0€ nights=1 — posible duplicado</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2016</v>
+        <v>2025</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>8</v>
@@ -1036,7 +1042,7 @@
       <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>histórico, no bloquea</t>
+          <t>Registro sin code ni checkin pero con ingreso — verificar</t>
         </is>
       </c>
     </row>
@@ -1063,14 +1069,14 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>7  2018-04-20-&gt;2018-04-24  &lt;-&gt;  7  2018-04-20-&gt;2018-04-24</t>
+          <t>12 Ashley 2016-08-01-&gt;2016-08-04  &lt;-&gt;  13 Eva 2016-08-03-&gt;2016-08-07</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H17" s="3" t="inlineStr"/>
       <c r="I17" s="3" t="inlineStr"/>
@@ -1104,14 +1110,14 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>26  2018-08-26-&gt;2018-08-30  &lt;-&gt;  21  2018-08-28-&gt;2018-08-30</t>
+          <t>7  2018-04-20-&gt;2018-04-24  &lt;-&gt;  7  2018-04-20-&gt;2018-04-24</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
         <v>2018</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H18" s="3" t="inlineStr"/>
       <c r="I18" s="3" t="inlineStr"/>
@@ -1145,14 +1151,14 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>29  2018-09-17-&gt;2018-09-26  &lt;-&gt;  27  2018-09-21-&gt;2018-09-30</t>
+          <t>26  2018-08-26-&gt;2018-08-30  &lt;-&gt;  21  2018-08-28-&gt;2018-08-30</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
         <v>2018</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H19" s="3" t="inlineStr"/>
       <c r="I19" s="3" t="inlineStr"/>
@@ -1186,7 +1192,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>27  2018-09-21-&gt;2018-09-30  &lt;-&gt;  30  2018-09-27-&gt;2018-10-01</t>
+          <t>29  2018-09-17-&gt;2018-09-26  &lt;-&gt;  27  2018-09-21-&gt;2018-09-30</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
@@ -1227,14 +1233,14 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>11 Dimitry 2019-06-01-&gt;2019-06-03  &lt;-&gt;  12 Giulia 2019-06-02-&gt;2019-06-06</t>
+          <t>27  2018-09-21-&gt;2018-09-30  &lt;-&gt;  30  2018-09-27-&gt;2018-10-01</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr"/>
@@ -1268,14 +1274,14 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>20 Anna 2019-07-18-&gt;2019-07-23  &lt;-&gt;  16 Jannik 2019-07-18-&gt;2019-07-20</t>
+          <t>11 Dimitry 2019-06-01-&gt;2019-06-03  &lt;-&gt;  12 Giulia 2019-06-02-&gt;2019-06-06</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
         <v>2019</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H22" s="3" t="inlineStr"/>
       <c r="I22" s="3" t="inlineStr"/>
@@ -1309,14 +1315,14 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>21 Agathe &amp; David 2020-08-01-&gt;2020-08-03  &lt;-&gt;   Miriam 2020-08-02-&gt;2020-08-08</t>
+          <t>20 Anna 2019-07-18-&gt;2019-07-23  &lt;-&gt;  16 Jannik 2019-07-18-&gt;2019-07-20</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H23" s="3" t="inlineStr"/>
       <c r="I23" s="3" t="inlineStr"/>
@@ -1350,11 +1356,11 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>15 Inmaculada Bennasar Martí 2021-08-09-&gt;2021-08-22  &lt;-&gt;  13 Anna-Lena Mayer 2021-08-21-&gt;2021-08-27</t>
+          <t>21 Agathe &amp; David 2020-08-01-&gt;2020-08-03  &lt;-&gt;   Miriam 2020-08-02-&gt;2020-08-08</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>8</v>
@@ -1391,7 +1397,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>13 Anna-Lena Mayer 2021-08-21-&gt;2021-08-27  &lt;-&gt;  16 Kim To 2021-08-23-&gt;2021-08-27</t>
+          <t>15 Inmaculada Bennasar Martí 2021-08-09-&gt;2021-08-22  &lt;-&gt;  13 Anna-Lena Mayer 2021-08-21-&gt;2021-08-27</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
@@ -1432,14 +1438,14 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>8 Diana Schmidt 2022-04-09-&gt;2022-04-17  &lt;-&gt;  10 Daniel Sawitzki 2022-04-16-&gt;2022-04-23</t>
+          <t>13 Anna-Lena Mayer 2021-08-21-&gt;2021-08-27  &lt;-&gt;  16 Kim To 2021-08-23-&gt;2021-08-27</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H26" s="3" t="inlineStr"/>
       <c r="I26" s="3" t="inlineStr"/>
@@ -1473,14 +1479,14 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>17 Mickael L. 2022-06-24-&gt;2022-06-30  &lt;-&gt;  22 Cristian Simon 2022-06-29-&gt;2022-07-01</t>
+          <t>8 Diana Schmidt 2022-04-09-&gt;2022-04-17  &lt;-&gt;  10 Daniel Sawitzki 2022-04-16-&gt;2022-04-23</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
         <v>2022</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H27" s="3" t="inlineStr"/>
       <c r="I27" s="3" t="inlineStr"/>
@@ -1514,14 +1520,14 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>31 Samira Wolfrum 2022-09-08-&gt;2022-09-21  &lt;-&gt;  32 Julian Bosch 2022-09-17-&gt;2022-09-20</t>
+          <t>17 Mickael L. 2022-06-24-&gt;2022-06-30  &lt;-&gt;  22 Cristian Simon 2022-06-29-&gt;2022-07-01</t>
         </is>
       </c>
       <c r="F28" s="3" t="n">
         <v>2022</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H28" s="3" t="inlineStr"/>
       <c r="I28" s="3" t="inlineStr"/>
@@ -1555,14 +1561,14 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>36 Mira Svozilek 2022-10-07-&gt;2022-10-13  &lt;-&gt;  35 Vincent Schneider CCG 2022-10-10-&gt;2022-10-17</t>
+          <t>31 Samira Wolfrum 2022-09-08-&gt;2022-09-21  &lt;-&gt;  32 Julian Bosch 2022-09-17-&gt;2022-09-20</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
         <v>2022</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H29" s="3" t="inlineStr"/>
       <c r="I29" s="3" t="inlineStr"/>
@@ -1596,14 +1602,14 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>41 Ansch Helbig 2022-12-25-&gt;2023-01-01  &lt;-&gt;  42 Jana Newiger-Dous 2022-12-31-&gt;2023-01-01</t>
+          <t>36 Mira Svozilek 2022-10-07-&gt;2022-10-13  &lt;-&gt;  35 Vincent Schneider CCG 2022-10-10-&gt;2022-10-17</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
         <v>2022</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H30" s="3" t="inlineStr"/>
       <c r="I30" s="3" t="inlineStr"/>
@@ -1637,14 +1643,14 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> John Curwen 2023-07-04-&gt;2023-07-07  &lt;-&gt;   Grace Munday 2023-07-06-&gt;2023-07-10</t>
+          <t>41 Ansch Helbig 2022-12-25-&gt;2023-01-01  &lt;-&gt;  42 Jana Newiger-Dous 2022-12-31-&gt;2023-01-01</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H31" s="3" t="inlineStr"/>
       <c r="I31" s="3" t="inlineStr"/>
@@ -1678,14 +1684,14 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Nancy Steinke 2023-11-01-&gt;2023-11-11  &lt;-&gt;   Rosie Hill 2023-11-01-&gt;2023-11-02</t>
+          <t xml:space="preserve"> John Curwen 2023-07-04-&gt;2023-07-07  &lt;-&gt;   Grace Munday 2023-07-06-&gt;2023-07-10</t>
         </is>
       </c>
       <c r="F32" s="3" t="n">
         <v>2023</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H32" s="3" t="inlineStr"/>
       <c r="I32" s="3" t="inlineStr"/>
@@ -1719,14 +1725,14 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Helene Meurillon 2023-12-01-&gt;2023-12-02  &lt;-&gt;   Janina Świderska 2023-12-01-&gt;2023-12-08</t>
+          <t xml:space="preserve"> Nancy Steinke 2023-11-01-&gt;2023-11-11  &lt;-&gt;   Rosie Hill 2023-11-01-&gt;2023-11-02</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
         <v>2023</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H33" s="3" t="inlineStr"/>
       <c r="I33" s="3" t="inlineStr"/>
@@ -1760,14 +1766,14 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Camille Marino 2024-08-01-&gt;2024-08-07  &lt;-&gt;   David Pérez Tamayo 2024-08-05-&gt;2024-08-08</t>
+          <t xml:space="preserve"> Helene Meurillon 2023-12-01-&gt;2023-12-02  &lt;-&gt;   Janina Świderska 2023-12-01-&gt;2023-12-08</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H34" s="3" t="inlineStr"/>
       <c r="I34" s="3" t="inlineStr"/>
@@ -1801,7 +1807,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Jonatan Díaz 2024-08-15-&gt;2024-08-20  &lt;-&gt;   Nina Scherer 2024-08-16-&gt;2024-08-17</t>
+          <t xml:space="preserve"> Camille Marino 2024-08-01-&gt;2024-08-07  &lt;-&gt;   David Pérez Tamayo 2024-08-05-&gt;2024-08-08</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
@@ -1842,7 +1848,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Giulio 2024-08-29-&gt;2024-09-02  &lt;-&gt;   Noemi Leggio 2024-08-29-&gt;2024-09-05</t>
+          <t xml:space="preserve"> Jonatan Díaz 2024-08-15-&gt;2024-08-20  &lt;-&gt;   Nina Scherer 2024-08-16-&gt;2024-08-17</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
@@ -1883,7 +1889,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Giulio 2024-08-29-&gt;2024-09-02  &lt;-&gt;   Paco Fernandez 2024-08-30-&gt;2024-09-01</t>
+          <t xml:space="preserve"> Giulio 2024-08-29-&gt;2024-09-02  &lt;-&gt;   Noemi Leggio 2024-08-29-&gt;2024-09-05</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
@@ -1924,7 +1930,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Giulio 2024-08-29-&gt;2024-09-02  &lt;-&gt;   Nina Scherer 2024-09-01-&gt;2024-09-07</t>
+          <t xml:space="preserve"> Giulio 2024-08-29-&gt;2024-09-02  &lt;-&gt;   Paco Fernandez 2024-08-30-&gt;2024-09-01</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
@@ -1965,7 +1971,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Noemi Leggio 2024-08-29-&gt;2024-09-05  &lt;-&gt;   Paco Fernandez 2024-08-30-&gt;2024-09-01</t>
+          <t xml:space="preserve"> Giulio 2024-08-29-&gt;2024-09-02  &lt;-&gt;   Nina Scherer 2024-09-01-&gt;2024-09-07</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
@@ -2006,7 +2012,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Noemi Leggio 2024-08-29-&gt;2024-09-05  &lt;-&gt;   Nina Scherer 2024-09-01-&gt;2024-09-07</t>
+          <t xml:space="preserve"> Noemi Leggio 2024-08-29-&gt;2024-09-05  &lt;-&gt;   Paco Fernandez 2024-08-30-&gt;2024-09-01</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
@@ -2047,14 +2053,14 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Geoff Walsh 2025-06-23-&gt;2025-07-02  &lt;-&gt;   Geoff Walsh 2025-07-01-&gt;2025-07-03</t>
+          <t xml:space="preserve"> Noemi Leggio 2024-08-29-&gt;2024-09-05  &lt;-&gt;   Nina Scherer 2024-09-01-&gt;2024-09-07</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H41" s="3" t="inlineStr"/>
       <c r="I41" s="3" t="inlineStr"/>
@@ -2068,81 +2074,89 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
+          <t>Solapes</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>AVISO</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Solape historico</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Geoff Walsh 2025-06-23-&gt;2025-07-02  &lt;-&gt;   Geoff Walsh 2025-07-01-&gt;2025-07-03</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H42" s="3" t="inlineStr"/>
+      <c r="I42" s="3" t="inlineStr"/>
+      <c r="J42" s="3" t="inlineStr"/>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>histórico, no bloquea</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
           <t>Totales_Anuales</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>AVISO</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Anual 2020</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>Ingresos=6378.0€  Noches=85  PM_ok=70.34  PM_dash=66.33  delta=5.7%</t>
         </is>
       </c>
-      <c r="F42" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>2020</v>
       </c>
-      <c r="G42" s="3" t="inlineStr"/>
-      <c r="H42" s="3" t="n">
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="n">
         <v>70.34</v>
       </c>
-      <c r="I42" s="3" t="n">
+      <c r="I43" s="3" t="n">
         <v>66.33</v>
       </c>
-      <c r="J42" s="3" t="n">
+      <c r="J43" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="K42" s="3" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>Baseline consistente</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>Ningún cambio respecto al baseline del 2026-05-26.</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr"/>
-      <c r="G43" s="4" t="inlineStr"/>
-      <c r="H43" s="4" t="inlineStr"/>
-      <c r="I43" s="4" t="inlineStr"/>
-      <c r="J43" s="4" t="inlineStr"/>
-      <c r="K43" s="4" t="inlineStr"/>
+      <c r="K43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Cancelaciones</t>
+          <t>Baseline</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -2157,17 +2171,15 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Tasa 2015</t>
+          <t>Baseline consistente</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>0/18 cancelaciones = 0.0%</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="n">
-        <v>2015</v>
-      </c>
+          <t>Ningún cambio respecto al baseline del 2026-06-18.</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="inlineStr"/>
       <c r="H44" s="4" t="inlineStr"/>
       <c r="I44" s="4" t="inlineStr"/>
@@ -2192,16 +2204,16 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Tasa 2016</t>
+          <t>Tasa 2015</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>0/19 cancelaciones = 0.0%</t>
+          <t>0/18 cancelaciones = 0.0%</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="G45" s="4" t="inlineStr"/>
       <c r="H45" s="4" t="inlineStr"/>
@@ -2227,16 +2239,16 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Tasa 2017</t>
+          <t>Tasa 2016</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>0/25 cancelaciones = 0.0%</t>
+          <t>0/19 cancelaciones = 0.0%</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="G46" s="4" t="inlineStr"/>
       <c r="H46" s="4" t="inlineStr"/>
@@ -2262,16 +2274,16 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Tasa 2018</t>
+          <t>Tasa 2017</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>0/44 cancelaciones = 0.0%</t>
+          <t>0/25 cancelaciones = 0.0%</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="G47" s="4" t="inlineStr"/>
       <c r="H47" s="4" t="inlineStr"/>
@@ -2297,16 +2309,16 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Tasa 2019</t>
+          <t>Tasa 2018</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>4/46 cancelaciones = 8.7%</t>
+          <t>0/44 cancelaciones = 0.0%</t>
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="G48" s="4" t="inlineStr"/>
       <c r="H48" s="4" t="inlineStr"/>
@@ -2332,16 +2344,16 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Tasa 2020</t>
+          <t>Tasa 2019</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>10/24 cancelaciones = 41.7%</t>
+          <t>4/46 cancelaciones = 8.7%</t>
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="G49" s="4" t="inlineStr"/>
       <c r="H49" s="4" t="inlineStr"/>
@@ -2367,16 +2379,16 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Tasa 2021</t>
+          <t>Tasa 2020</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>8/40 cancelaciones = 20.0%</t>
+          <t>10/24 cancelaciones = 41.7%</t>
         </is>
       </c>
       <c r="F50" s="4" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="G50" s="4" t="inlineStr"/>
       <c r="H50" s="4" t="inlineStr"/>
@@ -2402,16 +2414,16 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Tasa 2022</t>
+          <t>Tasa 2021</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>15/58 cancelaciones = 25.9%</t>
+          <t>8/40 cancelaciones = 20.0%</t>
         </is>
       </c>
       <c r="F51" s="4" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="G51" s="4" t="inlineStr"/>
       <c r="H51" s="4" t="inlineStr"/>
@@ -2437,16 +2449,16 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Tasa 2023</t>
+          <t>Tasa 2022</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>10/76 cancelaciones = 13.2%</t>
+          <t>15/58 cancelaciones = 25.9%</t>
         </is>
       </c>
       <c r="F52" s="4" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="G52" s="4" t="inlineStr"/>
       <c r="H52" s="4" t="inlineStr"/>
@@ -2472,16 +2484,16 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Tasa 2024</t>
+          <t>Tasa 2023</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>19/93 cancelaciones = 20.4%</t>
+          <t>10/76 cancelaciones = 13.2%</t>
         </is>
       </c>
       <c r="F53" s="4" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="G53" s="4" t="inlineStr"/>
       <c r="H53" s="4" t="inlineStr"/>
@@ -2507,16 +2519,16 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Tasa 2025</t>
+          <t>Tasa 2024</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>15/88 cancelaciones = 17.0%</t>
+          <t>19/93 cancelaciones = 20.4%</t>
         </is>
       </c>
       <c r="F54" s="4" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="G54" s="4" t="inlineStr"/>
       <c r="H54" s="4" t="inlineStr"/>
@@ -2542,16 +2554,16 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Tasa 2026</t>
+          <t>Tasa 2025</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>6/56 cancelaciones = 10.7%</t>
+          <t>15/88 cancelaciones = 17.0%</t>
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="G55" s="4" t="inlineStr"/>
       <c r="H55" s="4" t="inlineStr"/>
@@ -2577,16 +2589,16 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Tasa 2027</t>
+          <t>Tasa 2026</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>0/1 cancelaciones = 0.0%</t>
+          <t>10/65 cancelaciones = 15.4%</t>
         </is>
       </c>
       <c r="F56" s="4" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="G56" s="4" t="inlineStr"/>
       <c r="H56" s="4" t="inlineStr"/>
@@ -2597,7 +2609,7 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Conversion</t>
+          <t>Cancelaciones</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -2612,29 +2624,21 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>CVR 2018-01</t>
+          <t>Tasa 2027</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.3% (1/296)</t>
+          <t>0/4 cancelaciones = 0.0%</t>
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>2018</v>
-      </c>
-      <c r="G57" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H57" s="4" t="n">
-        <v>296</v>
-      </c>
-      <c r="I57" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" s="4" t="n">
-        <v>0.34</v>
-      </c>
+        <v>2027</v>
+      </c>
+      <c r="G57" s="4" t="inlineStr"/>
+      <c r="H57" s="4" t="inlineStr"/>
+      <c r="I57" s="4" t="inlineStr"/>
+      <c r="J57" s="4" t="inlineStr"/>
       <c r="K57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
@@ -2655,28 +2659,28 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>CVR 2018-02</t>
+          <t>CVR 2018-01</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>CVR=2.0% (12/602)</t>
+          <t>CVR=0.3% (1/296)</t>
         </is>
       </c>
       <c r="F58" s="4" t="n">
         <v>2018</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>602</v>
+        <v>296</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>1.99</v>
+        <v>0.34</v>
       </c>
       <c r="K58" s="4" t="inlineStr"/>
     </row>
@@ -2698,28 +2702,28 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>CVR 2018-03</t>
+          <t>CVR 2018-02</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>CVR=1.0% (6/614)</t>
+          <t>CVR=2.0% (12/602)</t>
         </is>
       </c>
       <c r="F59" s="4" t="n">
         <v>2018</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>0.98</v>
+        <v>1.99</v>
       </c>
       <c r="K59" s="4" t="inlineStr"/>
     </row>
@@ -2741,28 +2745,28 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>CVR 2018-04</t>
+          <t>CVR 2018-03</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>CVR=1.2% (4/340)</t>
+          <t>CVR=1.0% (6/614)</t>
         </is>
       </c>
       <c r="F60" s="4" t="n">
         <v>2018</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>340</v>
+        <v>614</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>1.18</v>
+        <v>0.98</v>
       </c>
       <c r="K60" s="4" t="inlineStr"/>
     </row>
@@ -2784,28 +2788,28 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>CVR 2018-05</t>
+          <t>CVR 2018-04</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>CVR=1.1% (5/455)</t>
+          <t>CVR=1.2% (4/340)</t>
         </is>
       </c>
       <c r="F61" s="4" t="n">
         <v>2018</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>455</v>
+        <v>340</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="K61" s="4" t="inlineStr"/>
     </row>
@@ -2827,28 +2831,28 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>CVR 2018-06</t>
+          <t>CVR 2018-05</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>CVR=1.5% (4/261)</t>
+          <t>CVR=1.1% (5/455)</t>
         </is>
       </c>
       <c r="F62" s="4" t="n">
         <v>2018</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>261</v>
+        <v>455</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>1.53</v>
+        <v>1.1</v>
       </c>
       <c r="K62" s="4" t="inlineStr"/>
     </row>
@@ -2870,28 +2874,28 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>CVR 2018-07</t>
+          <t>CVR 2018-06</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>CVR=1.6% (5/322)</t>
+          <t>CVR=1.5% (4/261)</t>
         </is>
       </c>
       <c r="F63" s="4" t="n">
         <v>2018</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>322</v>
+        <v>261</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="K63" s="4" t="inlineStr"/>
     </row>
@@ -2913,25 +2917,29 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>CVR 2018-08</t>
+          <t>CVR 2018-07</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>CVR=0% (historico, sin booking_date)</t>
+          <t>CVR=1.6% (5/322)</t>
         </is>
       </c>
       <c r="F64" s="4" t="n">
         <v>2018</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="I64" s="4" t="inlineStr"/>
-      <c r="J64" s="4" t="inlineStr"/>
+        <v>322</v>
+      </c>
+      <c r="I64" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J64" s="4" t="n">
+        <v>1.55</v>
+      </c>
       <c r="K64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
@@ -2952,7 +2960,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>CVR 2018-09</t>
+          <t>CVR 2018-08</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -2964,10 +2972,10 @@
         <v>2018</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>191</v>
+        <v>100</v>
       </c>
       <c r="I65" s="4" t="inlineStr"/>
       <c r="J65" s="4" t="inlineStr"/>
@@ -2991,29 +2999,25 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>CVR 2018-10</t>
+          <t>CVR 2018-09</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>CVR=1.8% (4/224)</t>
+          <t>CVR=0% (historico, sin booking_date)</t>
         </is>
       </c>
       <c r="F66" s="4" t="n">
         <v>2018</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>224</v>
-      </c>
-      <c r="I66" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J66" s="4" t="n">
-        <v>1.79</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="I66" s="4" t="inlineStr"/>
+      <c r="J66" s="4" t="inlineStr"/>
       <c r="K66" s="4" t="inlineStr"/>
     </row>
     <row r="67">
@@ -3034,28 +3038,28 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>CVR 2018-11</t>
+          <t>CVR 2018-10</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>CVR=1.0% (2/199)</t>
+          <t>CVR=1.8% (4/224)</t>
         </is>
       </c>
       <c r="F67" s="4" t="n">
         <v>2018</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="K67" s="4" t="inlineStr"/>
     </row>
@@ -3077,25 +3081,29 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>CVR 2018-12</t>
+          <t>CVR 2018-11</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>CVR=0% (historico, sin booking_date)</t>
+          <t>CVR=1.0% (2/199)</t>
         </is>
       </c>
       <c r="F68" s="4" t="n">
         <v>2018</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>104</v>
-      </c>
-      <c r="I68" s="4" t="inlineStr"/>
-      <c r="J68" s="4" t="inlineStr"/>
+        <v>199</v>
+      </c>
+      <c r="I68" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J68" s="4" t="n">
+        <v>1.01</v>
+      </c>
       <c r="K68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
@@ -3116,29 +3124,25 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>CVR 2019-01</t>
+          <t>CVR 2018-12</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>CVR=1.3% (3/232)</t>
+          <t>CVR=0% (historico, sin booking_date)</t>
         </is>
       </c>
       <c r="F69" s="4" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H69" s="4" t="n">
-        <v>232</v>
-      </c>
-      <c r="I69" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J69" s="4" t="n">
-        <v>1.29</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="I69" s="4" t="inlineStr"/>
+      <c r="J69" s="4" t="inlineStr"/>
       <c r="K69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
@@ -3159,28 +3163,28 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>CVR 2019-02</t>
+          <t>CVR 2019-01</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.9% (7/779)</t>
+          <t>CVR=1.3% (3/232)</t>
         </is>
       </c>
       <c r="F70" s="4" t="n">
         <v>2019</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>779</v>
+        <v>232</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>0.9</v>
+        <v>1.29</v>
       </c>
       <c r="K70" s="4" t="inlineStr"/>
     </row>
@@ -3202,28 +3206,28 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>CVR 2019-03</t>
+          <t>CVR 2019-02</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>CVR=1.3% (7/534)</t>
+          <t>CVR=0.9% (7/779)</t>
         </is>
       </c>
       <c r="F71" s="4" t="n">
         <v>2019</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>534</v>
+        <v>779</v>
       </c>
       <c r="I71" s="4" t="n">
         <v>7</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>1.31</v>
+        <v>0.9</v>
       </c>
       <c r="K71" s="4" t="inlineStr"/>
     </row>
@@ -3245,28 +3249,28 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>CVR 2019-04</t>
+          <t>CVR 2019-03</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.6% (4/634)</t>
+          <t>CVR=1.3% (7/534)</t>
         </is>
       </c>
       <c r="F72" s="4" t="n">
         <v>2019</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>634</v>
+        <v>534</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>0.63</v>
+        <v>1.31</v>
       </c>
       <c r="K72" s="4" t="inlineStr"/>
     </row>
@@ -3288,28 +3292,28 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>CVR 2019-05</t>
+          <t>CVR 2019-04</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.9% (5/562)</t>
+          <t>CVR=0.6% (4/634)</t>
         </is>
       </c>
       <c r="F73" s="4" t="n">
         <v>2019</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>562</v>
+        <v>634</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>0.89</v>
+        <v>0.63</v>
       </c>
       <c r="K73" s="4" t="inlineStr"/>
     </row>
@@ -3331,28 +3335,28 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>CVR 2019-06</t>
+          <t>CVR 2019-05</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.3% (1/388)</t>
+          <t>CVR=0.9% (5/562)</t>
         </is>
       </c>
       <c r="F74" s="4" t="n">
         <v>2019</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>388</v>
+        <v>562</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>0.26</v>
+        <v>0.89</v>
       </c>
       <c r="K74" s="4" t="inlineStr"/>
     </row>
@@ -3374,28 +3378,28 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>CVR 2019-07</t>
+          <t>CVR 2019-06</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.5% (2/441)</t>
+          <t>CVR=0.3% (1/388)</t>
         </is>
       </c>
       <c r="F75" s="4" t="n">
         <v>2019</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>441</v>
+        <v>388</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>0.45</v>
+        <v>0.26</v>
       </c>
       <c r="K75" s="4" t="inlineStr"/>
     </row>
@@ -3417,28 +3421,28 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>CVR 2019-08</t>
+          <t>CVR 2019-07</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>CVR=1.4% (5/350)</t>
+          <t>CVR=0.5% (2/441)</t>
         </is>
       </c>
       <c r="F76" s="4" t="n">
         <v>2019</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>350</v>
+        <v>441</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>1.43</v>
+        <v>0.45</v>
       </c>
       <c r="K76" s="4" t="inlineStr"/>
     </row>
@@ -3460,28 +3464,28 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>CVR 2019-09</t>
+          <t>CVR 2019-08</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.6% (2/355)</t>
+          <t>CVR=1.4% (5/350)</t>
         </is>
       </c>
       <c r="F77" s="4" t="n">
         <v>2019</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.43</v>
       </c>
       <c r="K77" s="4" t="inlineStr"/>
     </row>
@@ -3503,28 +3507,28 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>CVR 2019-10</t>
+          <t>CVR 2019-09</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>CVR=1.2% (4/336)</t>
+          <t>CVR=0.6% (2/355)</t>
         </is>
       </c>
       <c r="F78" s="4" t="n">
         <v>2019</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>1.19</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K78" s="4" t="inlineStr"/>
     </row>
@@ -3546,28 +3550,28 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>CVR 2019-11</t>
+          <t>CVR 2019-10</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.5% (2/442)</t>
+          <t>CVR=1.2% (4/336)</t>
         </is>
       </c>
       <c r="F79" s="4" t="n">
         <v>2019</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>442</v>
+        <v>336</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>0.45</v>
+        <v>1.19</v>
       </c>
       <c r="K79" s="4" t="inlineStr"/>
     </row>
@@ -3589,25 +3593,29 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>CVR 2019-12</t>
+          <t>CVR 2019-11</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>CVR=0% (historico, sin booking_date)</t>
+          <t>CVR=0.5% (2/442)</t>
         </is>
       </c>
       <c r="F80" s="4" t="n">
         <v>2019</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>1339</v>
-      </c>
-      <c r="I80" s="4" t="inlineStr"/>
-      <c r="J80" s="4" t="inlineStr"/>
+        <v>442</v>
+      </c>
+      <c r="I80" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J80" s="4" t="n">
+        <v>0.45</v>
+      </c>
       <c r="K80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
@@ -3628,29 +3636,25 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>CVR 2020-01</t>
+          <t>CVR 2019-12</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.1% (1/1448)</t>
+          <t>CVR=0% (historico, sin booking_date)</t>
         </is>
       </c>
       <c r="F81" s="4" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>1448</v>
-      </c>
-      <c r="I81" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J81" s="4" t="n">
-        <v>0.07000000000000001</v>
-      </c>
+        <v>1339</v>
+      </c>
+      <c r="I81" s="4" t="inlineStr"/>
+      <c r="J81" s="4" t="inlineStr"/>
       <c r="K81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
@@ -3671,28 +3675,28 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>CVR 2020-02</t>
+          <t>CVR 2020-01</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.2% (2/957)</t>
+          <t>CVR=0.1% (1/1448)</t>
         </is>
       </c>
       <c r="F82" s="4" t="n">
         <v>2020</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>957</v>
+        <v>1448</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>0.21</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K82" s="4" t="inlineStr"/>
     </row>
@@ -3714,28 +3718,28 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>CVR 2020-03</t>
+          <t>CVR 2020-02</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.3% (2/591)</t>
+          <t>CVR=0.2% (2/957)</t>
         </is>
       </c>
       <c r="F83" s="4" t="n">
         <v>2020</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>591</v>
+        <v>957</v>
       </c>
       <c r="I83" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>0.34</v>
+        <v>0.21</v>
       </c>
       <c r="K83" s="4" t="inlineStr"/>
     </row>
@@ -3757,25 +3761,29 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>CVR 2020-04</t>
+          <t>CVR 2020-03</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>CVR=0% (historico, sin booking_date)</t>
+          <t>CVR=0.3% (2/591)</t>
         </is>
       </c>
       <c r="F84" s="4" t="n">
         <v>2020</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>715</v>
-      </c>
-      <c r="I84" s="4" t="inlineStr"/>
-      <c r="J84" s="4" t="inlineStr"/>
+        <v>591</v>
+      </c>
+      <c r="I84" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J84" s="4" t="n">
+        <v>0.34</v>
+      </c>
       <c r="K84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
@@ -3796,7 +3804,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>CVR 2020-05</t>
+          <t>CVR 2020-04</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -3808,10 +3816,10 @@
         <v>2020</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H85" s="4" t="n">
-        <v>370</v>
+        <v>715</v>
       </c>
       <c r="I85" s="4" t="inlineStr"/>
       <c r="J85" s="4" t="inlineStr"/>
@@ -3835,29 +3843,25 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>CVR 2020-06</t>
+          <t>CVR 2020-05</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.1% (1/1235)</t>
+          <t>CVR=0% (historico, sin booking_date)</t>
         </is>
       </c>
       <c r="F86" s="4" t="n">
         <v>2020</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>1235</v>
-      </c>
-      <c r="I86" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J86" s="4" t="n">
-        <v>0.08</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="I86" s="4" t="inlineStr"/>
+      <c r="J86" s="4" t="inlineStr"/>
       <c r="K86" s="4" t="inlineStr"/>
     </row>
     <row r="87">
@@ -3878,28 +3882,28 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>CVR 2020-07</t>
+          <t>CVR 2020-06</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.3% (4/1141)</t>
+          <t>CVR=0.1% (1/1235)</t>
         </is>
       </c>
       <c r="F87" s="4" t="n">
         <v>2020</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>1141</v>
+        <v>1235</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>0.35</v>
+        <v>0.08</v>
       </c>
       <c r="K87" s="4" t="inlineStr"/>
     </row>
@@ -3921,25 +3925,29 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>CVR 2020-12</t>
+          <t>CVR 2020-07</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>CVR=0% (historico, sin booking_date)</t>
+          <t>CVR=0.3% (4/1141)</t>
         </is>
       </c>
       <c r="F88" s="4" t="n">
         <v>2020</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>162</v>
-      </c>
-      <c r="I88" s="4" t="inlineStr"/>
-      <c r="J88" s="4" t="inlineStr"/>
+        <v>1141</v>
+      </c>
+      <c r="I88" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J88" s="4" t="n">
+        <v>0.35</v>
+      </c>
       <c r="K88" s="4" t="inlineStr"/>
     </row>
     <row r="89">
@@ -3960,7 +3968,7 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>CVR 2021-01</t>
+          <t>CVR 2020-12</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -3969,13 +3977,13 @@
         </is>
       </c>
       <c r="F89" s="4" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H89" s="4" t="n">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="I89" s="4" t="inlineStr"/>
       <c r="J89" s="4" t="inlineStr"/>
@@ -3999,29 +4007,25 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>CVR 2021-02</t>
+          <t>CVR 2021-01</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.4% (1/231)</t>
+          <t>CVR=0% (historico, sin booking_date)</t>
         </is>
       </c>
       <c r="F90" s="4" t="n">
         <v>2021</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>231</v>
-      </c>
-      <c r="I90" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J90" s="4" t="n">
-        <v>0.43</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="I90" s="4" t="inlineStr"/>
+      <c r="J90" s="4" t="inlineStr"/>
       <c r="K90" s="4" t="inlineStr"/>
     </row>
     <row r="91">
@@ -4042,28 +4046,28 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>CVR 2021-03</t>
+          <t>CVR 2021-02</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>CVR=2.0% (9/438)</t>
+          <t>CVR=0.4% (1/231)</t>
         </is>
       </c>
       <c r="F91" s="4" t="n">
         <v>2021</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H91" s="4" t="n">
-        <v>438</v>
+        <v>231</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>2.05</v>
+        <v>0.43</v>
       </c>
       <c r="K91" s="4" t="inlineStr"/>
     </row>
@@ -4085,28 +4089,28 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>CVR 2021-04</t>
+          <t>CVR 2021-03</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.5% (3/579)</t>
+          <t>CVR=2.0% (9/438)</t>
         </is>
       </c>
       <c r="F92" s="4" t="n">
         <v>2021</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>579</v>
+        <v>438</v>
       </c>
       <c r="I92" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>0.52</v>
+        <v>2.05</v>
       </c>
       <c r="K92" s="4" t="inlineStr"/>
     </row>
@@ -4128,28 +4132,28 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>CVR 2021-05</t>
+          <t>CVR 2021-04</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>CVR=1.4% (8/554)</t>
+          <t>CVR=0.5% (3/579)</t>
         </is>
       </c>
       <c r="F93" s="4" t="n">
         <v>2021</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H93" s="4" t="n">
-        <v>554</v>
+        <v>579</v>
       </c>
       <c r="I93" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>1.44</v>
+        <v>0.52</v>
       </c>
       <c r="K93" s="4" t="inlineStr"/>
     </row>
@@ -4171,28 +4175,28 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>CVR 2021-06</t>
+          <t>CVR 2021-05</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>CVR=1.9% (5/266)</t>
+          <t>CVR=1.4% (8/554)</t>
         </is>
       </c>
       <c r="F94" s="4" t="n">
         <v>2021</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>266</v>
+        <v>554</v>
       </c>
       <c r="I94" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>1.88</v>
+        <v>1.44</v>
       </c>
       <c r="K94" s="4" t="inlineStr"/>
     </row>
@@ -4214,25 +4218,29 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>CVR 2021-07</t>
+          <t>CVR 2021-06</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>CVR=0% (historico, sin booking_date)</t>
+          <t>CVR=1.9% (5/266)</t>
         </is>
       </c>
       <c r="F95" s="4" t="n">
         <v>2021</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H95" s="4" t="n">
-        <v>242</v>
-      </c>
-      <c r="I95" s="4" t="inlineStr"/>
-      <c r="J95" s="4" t="inlineStr"/>
+        <v>266</v>
+      </c>
+      <c r="I95" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J95" s="4" t="n">
+        <v>1.88</v>
+      </c>
       <c r="K95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
@@ -4253,29 +4261,25 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>CVR 2021-08</t>
+          <t>CVR 2021-07</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.3% (1/313)</t>
+          <t>CVR=0% (historico, sin booking_date)</t>
         </is>
       </c>
       <c r="F96" s="4" t="n">
         <v>2021</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>313</v>
-      </c>
-      <c r="I96" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J96" s="4" t="n">
-        <v>0.32</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="I96" s="4" t="inlineStr"/>
+      <c r="J96" s="4" t="inlineStr"/>
       <c r="K96" s="4" t="inlineStr"/>
     </row>
     <row r="97">
@@ -4296,28 +4300,28 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>CVR 2021-09</t>
+          <t>CVR 2021-08</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.8% (3/400)</t>
+          <t>CVR=0.3% (1/313)</t>
         </is>
       </c>
       <c r="F97" s="4" t="n">
         <v>2021</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H97" s="4" t="n">
-        <v>400</v>
+        <v>313</v>
       </c>
       <c r="I97" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>0.75</v>
+        <v>0.32</v>
       </c>
       <c r="K97" s="4" t="inlineStr"/>
     </row>
@@ -4339,28 +4343,28 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>CVR 2021-10</t>
+          <t>CVR 2021-09</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.2% (1/403)</t>
+          <t>CVR=0.8% (3/400)</t>
         </is>
       </c>
       <c r="F98" s="4" t="n">
         <v>2021</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H98" s="4" t="n">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="I98" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J98" s="4" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="K98" s="4" t="inlineStr"/>
     </row>
@@ -4382,28 +4386,28 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>CVR 2021-11</t>
+          <t>CVR 2021-10</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.3% (1/317)</t>
+          <t>CVR=0.2% (1/403)</t>
         </is>
       </c>
       <c r="F99" s="4" t="n">
         <v>2021</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H99" s="4" t="n">
-        <v>317</v>
+        <v>403</v>
       </c>
       <c r="I99" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>0.32</v>
+        <v>0.25</v>
       </c>
       <c r="K99" s="4" t="inlineStr"/>
     </row>
@@ -4425,22 +4429,22 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>CVR 2021-12</t>
+          <t>CVR 2021-11</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.3% (1/311)</t>
+          <t>CVR=0.3% (1/317)</t>
         </is>
       </c>
       <c r="F100" s="4" t="n">
         <v>2021</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="I100" s="4" t="n">
         <v>1</v>
@@ -4468,28 +4472,28 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>CVR 2022-01</t>
+          <t>CVR 2021-12</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.1% (1/748)</t>
+          <t>CVR=0.3% (1/311)</t>
         </is>
       </c>
       <c r="F101" s="4" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H101" s="4" t="n">
-        <v>748</v>
+        <v>311</v>
       </c>
       <c r="I101" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>0.13</v>
+        <v>0.32</v>
       </c>
       <c r="K101" s="4" t="inlineStr"/>
     </row>
@@ -4511,28 +4515,28 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>CVR 2022-02</t>
+          <t>CVR 2022-01</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>CVR=1.1% (10/925)</t>
+          <t>CVR=0.1% (1/748)</t>
         </is>
       </c>
       <c r="F102" s="4" t="n">
         <v>2022</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>925</v>
+        <v>748</v>
       </c>
       <c r="I102" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>1.08</v>
+        <v>0.13</v>
       </c>
       <c r="K102" s="4" t="inlineStr"/>
     </row>
@@ -4554,28 +4558,28 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>CVR 2022-03</t>
+          <t>CVR 2022-02</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.9% (7/800)</t>
+          <t>CVR=1.1% (10/925)</t>
         </is>
       </c>
       <c r="F103" s="4" t="n">
         <v>2022</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H103" s="4" t="n">
-        <v>800</v>
+        <v>925</v>
       </c>
       <c r="I103" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>0.88</v>
+        <v>1.08</v>
       </c>
       <c r="K103" s="4" t="inlineStr"/>
     </row>
@@ -4597,28 +4601,28 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>CVR 2022-04</t>
+          <t>CVR 2022-03</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>CVR=1.1% (6/571)</t>
+          <t>CVR=0.9% (7/800)</t>
         </is>
       </c>
       <c r="F104" s="4" t="n">
         <v>2022</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>571</v>
+        <v>800</v>
       </c>
       <c r="I104" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>1.05</v>
+        <v>0.88</v>
       </c>
       <c r="K104" s="4" t="inlineStr"/>
     </row>
@@ -4640,28 +4644,28 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>CVR 2022-05</t>
+          <t>CVR 2022-04</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.5% (3/563)</t>
+          <t>CVR=1.1% (6/571)</t>
         </is>
       </c>
       <c r="F105" s="4" t="n">
         <v>2022</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H105" s="4" t="n">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="I105" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>0.53</v>
+        <v>1.05</v>
       </c>
       <c r="K105" s="4" t="inlineStr"/>
     </row>
@@ -4683,28 +4687,28 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>CVR 2022-06</t>
+          <t>CVR 2022-05</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.5% (3/613)</t>
+          <t>CVR=0.5% (3/563)</t>
         </is>
       </c>
       <c r="F106" s="4" t="n">
         <v>2022</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H106" s="4" t="n">
-        <v>613</v>
+        <v>563</v>
       </c>
       <c r="I106" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>0.49</v>
+        <v>0.53</v>
       </c>
       <c r="K106" s="4" t="inlineStr"/>
     </row>
@@ -4726,28 +4730,28 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>CVR 2022-07</t>
+          <t>CVR 2022-06</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.6% (3/519)</t>
+          <t>CVR=0.5% (3/613)</t>
         </is>
       </c>
       <c r="F107" s="4" t="n">
         <v>2022</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H107" s="4" t="n">
-        <v>519</v>
+        <v>613</v>
       </c>
       <c r="I107" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>0.58</v>
+        <v>0.49</v>
       </c>
       <c r="K107" s="4" t="inlineStr"/>
     </row>
@@ -4769,28 +4773,28 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>CVR 2022-08</t>
+          <t>CVR 2022-07</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.8% (3/390)</t>
+          <t>CVR=0.6% (3/519)</t>
         </is>
       </c>
       <c r="F108" s="4" t="n">
         <v>2022</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H108" s="4" t="n">
-        <v>390</v>
+        <v>519</v>
       </c>
       <c r="I108" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J108" s="4" t="n">
-        <v>0.77</v>
+        <v>0.58</v>
       </c>
       <c r="K108" s="4" t="inlineStr"/>
     </row>
@@ -4812,28 +4816,28 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>CVR 2022-09</t>
+          <t>CVR 2022-08</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.2% (1/418)</t>
+          <t>CVR=0.8% (3/390)</t>
         </is>
       </c>
       <c r="F109" s="4" t="n">
         <v>2022</v>
       </c>
       <c r="G109" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H109" s="4" t="n">
-        <v>418</v>
+        <v>390</v>
       </c>
       <c r="I109" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J109" s="4" t="n">
-        <v>0.24</v>
+        <v>0.77</v>
       </c>
       <c r="K109" s="4" t="inlineStr"/>
     </row>
@@ -4855,28 +4859,28 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>CVR 2022-10</t>
+          <t>CVR 2022-09</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.8% (5/633)</t>
+          <t>CVR=0.2% (1/418)</t>
         </is>
       </c>
       <c r="F110" s="4" t="n">
         <v>2022</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H110" s="4" t="n">
-        <v>633</v>
+        <v>418</v>
       </c>
       <c r="I110" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>0.79</v>
+        <v>0.24</v>
       </c>
       <c r="K110" s="4" t="inlineStr"/>
     </row>
@@ -4898,28 +4902,28 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>CVR 2022-11</t>
+          <t>CVR 2022-10</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.2% (1/507)</t>
+          <t>CVR=0.8% (5/633)</t>
         </is>
       </c>
       <c r="F111" s="4" t="n">
         <v>2022</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H111" s="4" t="n">
-        <v>507</v>
+        <v>633</v>
       </c>
       <c r="I111" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>0.2</v>
+        <v>0.79</v>
       </c>
       <c r="K111" s="4" t="inlineStr"/>
     </row>
@@ -4941,28 +4945,28 @@
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>CVR 2022-12</t>
+          <t>CVR 2022-11</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.9% (5/538)</t>
+          <t>CVR=0.2% (1/507)</t>
         </is>
       </c>
       <c r="F112" s="4" t="n">
         <v>2022</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H112" s="4" t="n">
-        <v>538</v>
+        <v>507</v>
       </c>
       <c r="I112" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>0.93</v>
+        <v>0.2</v>
       </c>
       <c r="K112" s="4" t="inlineStr"/>
     </row>
@@ -4984,28 +4988,28 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>CVR 2023-01</t>
+          <t>CVR 2022-12</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.6% (11/1747)</t>
+          <t>CVR=0.9% (5/538)</t>
         </is>
       </c>
       <c r="F113" s="4" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="G113" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H113" s="4" t="n">
-        <v>1747</v>
+        <v>538</v>
       </c>
       <c r="I113" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>0.63</v>
+        <v>0.93</v>
       </c>
       <c r="K113" s="4" t="inlineStr"/>
     </row>
@@ -5027,28 +5031,28 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>CVR 2023-02</t>
+          <t>CVR 2023-01</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.8% (7/929)</t>
+          <t>CVR=0.6% (11/1747)</t>
         </is>
       </c>
       <c r="F114" s="4" t="n">
         <v>2023</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H114" s="4" t="n">
-        <v>929</v>
+        <v>1747</v>
       </c>
       <c r="I114" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>0.75</v>
+        <v>0.63</v>
       </c>
       <c r="K114" s="4" t="inlineStr"/>
     </row>
@@ -5070,28 +5074,28 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>CVR 2023-03</t>
+          <t>CVR 2023-02</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.6% (9/1569)</t>
+          <t>CVR=0.8% (7/929)</t>
         </is>
       </c>
       <c r="F115" s="4" t="n">
         <v>2023</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H115" s="4" t="n">
-        <v>1569</v>
+        <v>929</v>
       </c>
       <c r="I115" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="K115" s="4" t="inlineStr"/>
     </row>
@@ -5113,28 +5117,28 @@
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>CVR 2023-04</t>
+          <t>CVR 2023-03</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.9% (7/747)</t>
+          <t>CVR=0.6% (9/1569)</t>
         </is>
       </c>
       <c r="F116" s="4" t="n">
         <v>2023</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H116" s="4" t="n">
-        <v>747</v>
+        <v>1569</v>
       </c>
       <c r="I116" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.57</v>
       </c>
       <c r="K116" s="4" t="inlineStr"/>
     </row>
@@ -5156,28 +5160,28 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>CVR 2023-05</t>
+          <t>CVR 2023-04</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.9% (5/542)</t>
+          <t>CVR=0.9% (7/747)</t>
         </is>
       </c>
       <c r="F117" s="4" t="n">
         <v>2023</v>
       </c>
       <c r="G117" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H117" s="4" t="n">
-        <v>542</v>
+        <v>747</v>
       </c>
       <c r="I117" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K117" s="4" t="inlineStr"/>
     </row>
@@ -5199,28 +5203,28 @@
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>CVR 2023-06</t>
+          <t>CVR 2023-05</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.6% (2/347)</t>
+          <t>CVR=0.9% (5/542)</t>
         </is>
       </c>
       <c r="F118" s="4" t="n">
         <v>2023</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H118" s="4" t="n">
-        <v>347</v>
+        <v>542</v>
       </c>
       <c r="I118" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>0.58</v>
+        <v>0.92</v>
       </c>
       <c r="K118" s="4" t="inlineStr"/>
     </row>
@@ -5242,28 +5246,28 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>CVR 2023-07</t>
+          <t>CVR 2023-06</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.9% (3/317)</t>
+          <t>CVR=0.6% (2/347)</t>
         </is>
       </c>
       <c r="F119" s="4" t="n">
         <v>2023</v>
       </c>
       <c r="G119" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H119" s="4" t="n">
-        <v>317</v>
+        <v>347</v>
       </c>
       <c r="I119" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>0.95</v>
+        <v>0.58</v>
       </c>
       <c r="K119" s="4" t="inlineStr"/>
     </row>
@@ -5285,25 +5289,29 @@
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>CVR 2023-08</t>
+          <t>CVR 2023-07</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>CVR=0% (historico, sin booking_date)</t>
+          <t>CVR=0.9% (3/317)</t>
         </is>
       </c>
       <c r="F120" s="4" t="n">
         <v>2023</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H120" s="4" t="n">
-        <v>408</v>
-      </c>
-      <c r="I120" s="4" t="inlineStr"/>
-      <c r="J120" s="4" t="inlineStr"/>
+        <v>317</v>
+      </c>
+      <c r="I120" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J120" s="4" t="n">
+        <v>0.95</v>
+      </c>
       <c r="K120" s="4" t="inlineStr"/>
     </row>
     <row r="121">
@@ -5324,29 +5332,25 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>CVR 2023-09</t>
+          <t>CVR 2023-08</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.9% (5/572)</t>
+          <t>CVR=0% (historico, sin booking_date)</t>
         </is>
       </c>
       <c r="F121" s="4" t="n">
         <v>2023</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H121" s="4" t="n">
-        <v>572</v>
-      </c>
-      <c r="I121" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J121" s="4" t="n">
-        <v>0.87</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="I121" s="4" t="inlineStr"/>
+      <c r="J121" s="4" t="inlineStr"/>
       <c r="K121" s="4" t="inlineStr"/>
     </row>
     <row r="122">
@@ -5367,28 +5371,28 @@
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>CVR 2023-10</t>
+          <t>CVR 2023-09</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.7% (8/1128)</t>
+          <t>CVR=0.9% (5/572)</t>
         </is>
       </c>
       <c r="F122" s="4" t="n">
         <v>2023</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H122" s="4" t="n">
-        <v>1128</v>
+        <v>572</v>
       </c>
       <c r="I122" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="K122" s="4" t="inlineStr"/>
     </row>
@@ -5410,28 +5414,28 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>CVR 2023-11</t>
+          <t>CVR 2023-10</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.9% (8/924)</t>
+          <t>CVR=0.7% (8/1128)</t>
         </is>
       </c>
       <c r="F123" s="4" t="n">
         <v>2023</v>
       </c>
       <c r="G123" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H123" s="4" t="n">
-        <v>924</v>
+        <v>1128</v>
       </c>
       <c r="I123" s="4" t="n">
         <v>8</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>0.87</v>
+        <v>0.71</v>
       </c>
       <c r="K123" s="4" t="inlineStr"/>
     </row>
@@ -5453,28 +5457,28 @@
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>CVR 2023-12</t>
+          <t>CVR 2023-11</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.8% (8/1013)</t>
+          <t>CVR=0.9% (8/924)</t>
         </is>
       </c>
       <c r="F124" s="4" t="n">
         <v>2023</v>
       </c>
       <c r="G124" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H124" s="4" t="n">
-        <v>1013</v>
+        <v>924</v>
       </c>
       <c r="I124" s="4" t="n">
         <v>8</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="K124" s="4" t="inlineStr"/>
     </row>
@@ -5496,28 +5500,28 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>CVR 2024-01</t>
+          <t>CVR 2023-12</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>CVR=1.1% (14/1231)</t>
+          <t>CVR=0.8% (8/1013)</t>
         </is>
       </c>
       <c r="F125" s="4" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="G125" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H125" s="4" t="n">
-        <v>1231</v>
+        <v>1013</v>
       </c>
       <c r="I125" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>1.14</v>
+        <v>0.79</v>
       </c>
       <c r="K125" s="4" t="inlineStr"/>
     </row>
@@ -5539,28 +5543,28 @@
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>CVR 2024-02</t>
+          <t>CVR 2024-01</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>CVR=1.4% (7/507)</t>
+          <t>CVR=1.1% (14/1231)</t>
         </is>
       </c>
       <c r="F126" s="4" t="n">
         <v>2024</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H126" s="4" t="n">
-        <v>507</v>
+        <v>1231</v>
       </c>
       <c r="I126" s="4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="K126" s="4" t="inlineStr"/>
     </row>
@@ -5582,28 +5586,28 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>CVR 2024-03</t>
+          <t>CVR 2024-02</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>CVR=1.6% (10/623)</t>
+          <t>CVR=1.4% (7/507)</t>
         </is>
       </c>
       <c r="F127" s="4" t="n">
         <v>2024</v>
       </c>
       <c r="G127" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H127" s="4" t="n">
-        <v>623</v>
+        <v>507</v>
       </c>
       <c r="I127" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="K127" s="4" t="inlineStr"/>
     </row>
@@ -5625,28 +5629,28 @@
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>CVR 2024-04</t>
+          <t>CVR 2024-03</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.3% (1/337)</t>
+          <t>CVR=1.6% (10/623)</t>
         </is>
       </c>
       <c r="F128" s="4" t="n">
         <v>2024</v>
       </c>
       <c r="G128" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H128" s="4" t="n">
-        <v>337</v>
+        <v>623</v>
       </c>
       <c r="I128" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>0.3</v>
+        <v>1.61</v>
       </c>
       <c r="K128" s="4" t="inlineStr"/>
     </row>
@@ -5668,28 +5672,28 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>CVR 2024-05</t>
+          <t>CVR 2024-04</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.5% (2/422)</t>
+          <t>CVR=0.3% (1/337)</t>
         </is>
       </c>
       <c r="F129" s="4" t="n">
         <v>2024</v>
       </c>
       <c r="G129" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H129" s="4" t="n">
-        <v>422</v>
+        <v>337</v>
       </c>
       <c r="I129" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>0.47</v>
+        <v>0.3</v>
       </c>
       <c r="K129" s="4" t="inlineStr"/>
     </row>
@@ -5711,28 +5715,28 @@
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>CVR 2024-06</t>
+          <t>CVR 2024-05</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.5% (2/440)</t>
+          <t>CVR=0.5% (2/422)</t>
         </is>
       </c>
       <c r="F130" s="4" t="n">
         <v>2024</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H130" s="4" t="n">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="I130" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J130" s="4" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="K130" s="4" t="inlineStr"/>
     </row>
@@ -5754,28 +5758,28 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>CVR 2024-07</t>
+          <t>CVR 2024-06</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.8% (7/915)</t>
+          <t>CVR=0.5% (2/440)</t>
         </is>
       </c>
       <c r="F131" s="4" t="n">
         <v>2024</v>
       </c>
       <c r="G131" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H131" s="4" t="n">
-        <v>915</v>
+        <v>440</v>
       </c>
       <c r="I131" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>0.77</v>
+        <v>0.45</v>
       </c>
       <c r="K131" s="4" t="inlineStr"/>
     </row>
@@ -5797,28 +5801,28 @@
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>CVR 2024-08</t>
+          <t>CVR 2024-07</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.4% (3/809)</t>
+          <t>CVR=0.8% (7/915)</t>
         </is>
       </c>
       <c r="F132" s="4" t="n">
         <v>2024</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H132" s="4" t="n">
-        <v>809</v>
+        <v>915</v>
       </c>
       <c r="I132" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>0.37</v>
+        <v>0.77</v>
       </c>
       <c r="K132" s="4" t="inlineStr"/>
     </row>
@@ -5840,28 +5844,28 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>CVR 2024-09</t>
+          <t>CVR 2024-08</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.7% (7/1037)</t>
+          <t>CVR=0.4% (3/809)</t>
         </is>
       </c>
       <c r="F133" s="4" t="n">
         <v>2024</v>
       </c>
       <c r="G133" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H133" s="4" t="n">
-        <v>1037</v>
+        <v>809</v>
       </c>
       <c r="I133" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>0.68</v>
+        <v>0.37</v>
       </c>
       <c r="K133" s="4" t="inlineStr"/>
     </row>
@@ -5883,28 +5887,28 @@
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>CVR 2024-10</t>
+          <t>CVR 2024-09</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>CVR=1.1% (13/1136)</t>
+          <t>CVR=0.7% (7/1037)</t>
         </is>
       </c>
       <c r="F134" s="4" t="n">
         <v>2024</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H134" s="4" t="n">
-        <v>1136</v>
+        <v>1037</v>
       </c>
       <c r="I134" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>1.14</v>
+        <v>0.68</v>
       </c>
       <c r="K134" s="4" t="inlineStr"/>
     </row>
@@ -5926,28 +5930,28 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>CVR 2024-11</t>
+          <t>CVR 2024-10</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.8% (6/709)</t>
+          <t>CVR=1.1% (12/1136)</t>
         </is>
       </c>
       <c r="F135" s="4" t="n">
         <v>2024</v>
       </c>
       <c r="G135" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H135" s="4" t="n">
-        <v>709</v>
+        <v>1136</v>
       </c>
       <c r="I135" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>0.85</v>
+        <v>1.06</v>
       </c>
       <c r="K135" s="4" t="inlineStr"/>
     </row>
@@ -5969,28 +5973,28 @@
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>CVR 2024-12</t>
+          <t>CVR 2024-11</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>CVR=1.4% (11/765)</t>
+          <t>CVR=0.8% (6/709)</t>
         </is>
       </c>
       <c r="F136" s="4" t="n">
         <v>2024</v>
       </c>
       <c r="G136" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H136" s="4" t="n">
-        <v>765</v>
+        <v>709</v>
       </c>
       <c r="I136" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J136" s="4" t="n">
-        <v>1.44</v>
+        <v>0.85</v>
       </c>
       <c r="K136" s="4" t="inlineStr"/>
     </row>
@@ -6012,28 +6016,28 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>CVR 2025-01</t>
+          <t>CVR 2024-12</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.9% (10/1168)</t>
+          <t>CVR=1.4% (11/765)</t>
         </is>
       </c>
       <c r="F137" s="4" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="G137" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H137" s="4" t="n">
-        <v>1168</v>
+        <v>765</v>
       </c>
       <c r="I137" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>0.86</v>
+        <v>1.44</v>
       </c>
       <c r="K137" s="4" t="inlineStr"/>
     </row>
@@ -6055,28 +6059,28 @@
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>CVR 2025-02</t>
+          <t>CVR 2025-01</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.9% (7/809)</t>
+          <t>CVR=0.9% (10/1168)</t>
         </is>
       </c>
       <c r="F138" s="4" t="n">
         <v>2025</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H138" s="4" t="n">
-        <v>809</v>
+        <v>1168</v>
       </c>
       <c r="I138" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="K138" s="4" t="inlineStr"/>
     </row>
@@ -6098,28 +6102,28 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>CVR 2025-03</t>
+          <t>CVR 2025-02</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>CVR=1.1% (9/792)</t>
+          <t>CVR=0.9% (7/809)</t>
         </is>
       </c>
       <c r="F139" s="4" t="n">
         <v>2025</v>
       </c>
       <c r="G139" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H139" s="4" t="n">
-        <v>792</v>
+        <v>809</v>
       </c>
       <c r="I139" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J139" s="4" t="n">
-        <v>1.14</v>
+        <v>0.87</v>
       </c>
       <c r="K139" s="4" t="inlineStr"/>
     </row>
@@ -6141,28 +6145,28 @@
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>CVR 2025-04</t>
+          <t>CVR 2025-03</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.7% (3/427)</t>
+          <t>CVR=1.1% (9/792)</t>
         </is>
       </c>
       <c r="F140" s="4" t="n">
         <v>2025</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H140" s="4" t="n">
-        <v>427</v>
+        <v>792</v>
       </c>
       <c r="I140" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>0.7</v>
+        <v>1.14</v>
       </c>
       <c r="K140" s="4" t="inlineStr"/>
     </row>
@@ -6184,28 +6188,28 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>CVR 2025-05</t>
+          <t>CVR 2025-04</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.5% (3/591)</t>
+          <t>CVR=0.7% (3/427)</t>
         </is>
       </c>
       <c r="F141" s="4" t="n">
         <v>2025</v>
       </c>
       <c r="G141" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H141" s="4" t="n">
-        <v>591</v>
+        <v>427</v>
       </c>
       <c r="I141" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J141" s="4" t="n">
-        <v>0.51</v>
+        <v>0.7</v>
       </c>
       <c r="K141" s="4" t="inlineStr"/>
     </row>
@@ -6227,28 +6231,28 @@
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>CVR 2025-06</t>
+          <t>CVR 2025-05</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.3% (2/646)</t>
+          <t>CVR=0.5% (3/591)</t>
         </is>
       </c>
       <c r="F142" s="4" t="n">
         <v>2025</v>
       </c>
       <c r="G142" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H142" s="4" t="n">
-        <v>646</v>
+        <v>591</v>
       </c>
       <c r="I142" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J142" s="4" t="n">
-        <v>0.31</v>
+        <v>0.51</v>
       </c>
       <c r="K142" s="4" t="inlineStr"/>
     </row>
@@ -6270,28 +6274,28 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>CVR 2025-07</t>
+          <t>CVR 2025-06</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.7% (8/1147)</t>
+          <t>CVR=0.3% (2/646)</t>
         </is>
       </c>
       <c r="F143" s="4" t="n">
         <v>2025</v>
       </c>
       <c r="G143" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H143" s="4" t="n">
-        <v>1147</v>
+        <v>646</v>
       </c>
       <c r="I143" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J143" s="4" t="n">
-        <v>0.7</v>
+        <v>0.31</v>
       </c>
       <c r="K143" s="4" t="inlineStr"/>
     </row>
@@ -6313,28 +6317,28 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>CVR 2025-08</t>
+          <t>CVR 2025-07</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.6% (6/1005)</t>
+          <t>CVR=0.7% (8/1147)</t>
         </is>
       </c>
       <c r="F144" s="4" t="n">
         <v>2025</v>
       </c>
       <c r="G144" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H144" s="4" t="n">
+        <v>1147</v>
+      </c>
+      <c r="I144" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="H144" s="4" t="n">
-        <v>1005</v>
-      </c>
-      <c r="I144" s="4" t="n">
-        <v>6</v>
-      </c>
       <c r="J144" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K144" s="4" t="inlineStr"/>
     </row>
@@ -6356,28 +6360,28 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>CVR 2025-09</t>
+          <t>CVR 2025-08</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.8% (7/880)</t>
+          <t>CVR=0.6% (6/1005)</t>
         </is>
       </c>
       <c r="F145" s="4" t="n">
         <v>2025</v>
       </c>
       <c r="G145" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H145" s="4" t="n">
-        <v>880</v>
+        <v>1005</v>
       </c>
       <c r="I145" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J145" s="4" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K145" s="4" t="inlineStr"/>
     </row>
@@ -6399,28 +6403,28 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>CVR 2025-10</t>
+          <t>CVR 2025-09</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.2% (2/1156)</t>
+          <t>CVR=0.7% (6/880)</t>
         </is>
       </c>
       <c r="F146" s="4" t="n">
         <v>2025</v>
       </c>
       <c r="G146" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H146" s="4" t="n">
-        <v>1156</v>
+        <v>880</v>
       </c>
       <c r="I146" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J146" s="4" t="n">
-        <v>0.17</v>
+        <v>0.68</v>
       </c>
       <c r="K146" s="4" t="inlineStr"/>
     </row>
@@ -6442,28 +6446,28 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>CVR 2025-11</t>
+          <t>CVR 2025-10</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>CVR=1.2% (11/921)</t>
+          <t>CVR=0.2% (2/1156)</t>
         </is>
       </c>
       <c r="F147" s="4" t="n">
         <v>2025</v>
       </c>
       <c r="G147" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H147" s="4" t="n">
-        <v>921</v>
+        <v>1156</v>
       </c>
       <c r="I147" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J147" s="4" t="n">
-        <v>1.19</v>
+        <v>0.17</v>
       </c>
       <c r="K147" s="4" t="inlineStr"/>
     </row>
@@ -6485,28 +6489,28 @@
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>CVR 2025-12</t>
+          <t>CVR 2025-11</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>CVR=1.2% (8/654)</t>
+          <t>CVR=1.0% (9/921)</t>
         </is>
       </c>
       <c r="F148" s="4" t="n">
         <v>2025</v>
       </c>
       <c r="G148" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H148" s="4" t="n">
-        <v>654</v>
+        <v>921</v>
       </c>
       <c r="I148" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J148" s="4" t="n">
-        <v>1.22</v>
+        <v>0.98</v>
       </c>
       <c r="K148" s="4" t="inlineStr"/>
     </row>
@@ -6528,28 +6532,28 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>CVR 2026-01</t>
+          <t>CVR 2025-12</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.9% (6/675)</t>
+          <t>CVR=1.2% (8/654)</t>
         </is>
       </c>
       <c r="F149" s="4" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="G149" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H149" s="4" t="n">
-        <v>675</v>
+        <v>654</v>
       </c>
       <c r="I149" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J149" s="4" t="n">
-        <v>0.89</v>
+        <v>1.22</v>
       </c>
       <c r="K149" s="4" t="inlineStr"/>
     </row>
@@ -6571,28 +6575,28 @@
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>CVR 2026-02</t>
+          <t>CVR 2026-01</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.5% (4/750)</t>
+          <t>CVR=0.9% (6/675)</t>
         </is>
       </c>
       <c r="F150" s="4" t="n">
         <v>2026</v>
       </c>
       <c r="G150" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H150" s="4" t="n">
-        <v>750</v>
+        <v>675</v>
       </c>
       <c r="I150" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J150" s="4" t="n">
-        <v>0.53</v>
+        <v>0.89</v>
       </c>
       <c r="K150" s="4" t="inlineStr"/>
     </row>
@@ -6614,28 +6618,28 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>CVR 2026-03</t>
+          <t>CVR 2026-02</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.5% (5/1041)</t>
+          <t>CVR=0.5% (4/750)</t>
         </is>
       </c>
       <c r="F151" s="4" t="n">
         <v>2026</v>
       </c>
       <c r="G151" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H151" s="4" t="n">
-        <v>1041</v>
+        <v>750</v>
       </c>
       <c r="I151" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J151" s="4" t="n">
-        <v>0.48</v>
+        <v>0.53</v>
       </c>
       <c r="K151" s="4" t="inlineStr"/>
     </row>
@@ -6657,35 +6661,35 @@
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>CVR 2026-04</t>
+          <t>CVR 2026-03</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>CVR=0.7% (9/1226)</t>
+          <t>CVR=0.5% (5/1041)</t>
         </is>
       </c>
       <c r="F152" s="4" t="n">
         <v>2026</v>
       </c>
       <c r="G152" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H152" s="4" t="n">
-        <v>1226</v>
+        <v>1041</v>
       </c>
       <c r="I152" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J152" s="4" t="n">
-        <v>0.73</v>
+        <v>0.48</v>
       </c>
       <c r="K152" s="4" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>Distorsion_CrossMonth</t>
+          <t>Conversion</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
@@ -6700,25 +6704,35 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Sin distorsiones graves</t>
+          <t>CVR 2026-04</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>Ninguna reserva cross-month distorsiona un mes significativamente</t>
-        </is>
-      </c>
-      <c r="F153" s="4" t="inlineStr"/>
-      <c r="G153" s="4" t="inlineStr"/>
-      <c r="H153" s="4" t="inlineStr"/>
-      <c r="I153" s="4" t="inlineStr"/>
-      <c r="J153" s="4" t="inlineStr"/>
+          <t>CVR=0.7% (9/1226)</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G153" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H153" s="4" t="n">
+        <v>1226</v>
+      </c>
+      <c r="I153" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J153" s="4" t="n">
+        <v>0.73</v>
+      </c>
       <c r="K153" s="4" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>Integridad</t>
+          <t>Conversion</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
@@ -6733,25 +6747,35 @@
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Integridad OK</t>
+          <t>CVR 2026-05</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>Sin anomalias detectadas</t>
-        </is>
-      </c>
-      <c r="F154" s="4" t="inlineStr"/>
-      <c r="G154" s="4" t="inlineStr"/>
-      <c r="H154" s="4" t="inlineStr"/>
-      <c r="I154" s="4" t="inlineStr"/>
-      <c r="J154" s="4" t="inlineStr"/>
+          <t>CVR=0.2% (3/1273)</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G154" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H154" s="4" t="n">
+        <v>1273</v>
+      </c>
+      <c r="I154" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J154" s="4" t="n">
+        <v>0.24</v>
+      </c>
       <c r="K154" s="4" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>Lead_Time</t>
+          <t>Integridad</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
@@ -6766,25 +6790,19 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>PM lead &lt;7d</t>
+          <t>Integridad OK</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>n=34  PM_correcto=55.87  PM_dashboard=54.44  delta=2.6%</t>
+          <t>Sin anomalias detectadas</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr"/>
       <c r="G155" s="4" t="inlineStr"/>
-      <c r="H155" s="4" t="n">
-        <v>55.87</v>
-      </c>
-      <c r="I155" s="4" t="n">
-        <v>54.44</v>
-      </c>
-      <c r="J155" s="4" t="n">
-        <v>2.6</v>
-      </c>
+      <c r="H155" s="4" t="inlineStr"/>
+      <c r="I155" s="4" t="inlineStr"/>
+      <c r="J155" s="4" t="inlineStr"/>
       <c r="K155" s="4" t="inlineStr"/>
     </row>
     <row r="156">
@@ -6805,24 +6823,24 @@
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>PM lead 7-30d</t>
+          <t>PM lead &lt;7d</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>n=106  PM_correcto=54.66  PM_dashboard=53.37  delta=2.4%</t>
+          <t>n=34  PM_correcto=55.87  PM_dashboard=54.44  delta=2.6%</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr"/>
       <c r="G156" s="4" t="inlineStr"/>
       <c r="H156" s="4" t="n">
-        <v>54.66</v>
+        <v>55.87</v>
       </c>
       <c r="I156" s="4" t="n">
-        <v>53.37</v>
+        <v>54.44</v>
       </c>
       <c r="J156" s="4" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="K156" s="4" t="inlineStr"/>
     </row>
@@ -6844,21 +6862,21 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>PM lead 30-90d</t>
+          <t>PM lead 7-30d</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>n=159  PM_correcto=64.65  PM_dashboard=63.43  delta=1.9%</t>
+          <t>n=112  PM_correcto=55.07  PM_dashboard=54.00  delta=1.9%</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr"/>
       <c r="G157" s="4" t="inlineStr"/>
       <c r="H157" s="4" t="n">
-        <v>64.65000000000001</v>
+        <v>55.07</v>
       </c>
       <c r="I157" s="4" t="n">
-        <v>63.43</v>
+        <v>54</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>1.9</v>
@@ -6883,29 +6901,31 @@
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>PM lead &gt;90d</t>
+          <t>PM lead 30-90d</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>n=183  PM_correcto=77.35  PM_dashboard=77.34  delta=0.0%</t>
+          <t>n=162  PM_correcto=65.55  PM_dashboard=64.35  delta=1.8%</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr"/>
       <c r="G158" s="4" t="inlineStr"/>
       <c r="H158" s="4" t="n">
-        <v>77.34999999999999</v>
+        <v>65.55</v>
       </c>
       <c r="I158" s="4" t="n">
-        <v>77.34</v>
-      </c>
-      <c r="J158" s="4" t="inlineStr"/>
+        <v>64.34999999999999</v>
+      </c>
+      <c r="J158" s="4" t="n">
+        <v>1.8</v>
+      </c>
       <c r="K158" s="4" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>Superhost</t>
+          <t>Lead_Time</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
@@ -6920,30 +6940,26 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Eval 2025-01-01</t>
+          <t>PM lead &gt;90d</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>Estancias=71  rating=0.00(0 reviews)  canc_total=20.2%</t>
-        </is>
-      </c>
-      <c r="F159" s="4" t="n">
-        <v>2025</v>
-      </c>
-      <c r="G159" s="4" t="n">
-        <v>1</v>
-      </c>
+          <t>n=182  PM_correcto=77.89  PM_dashboard=78.18  delta=0.4%</t>
+        </is>
+      </c>
+      <c r="F159" s="4" t="inlineStr"/>
+      <c r="G159" s="4" t="inlineStr"/>
       <c r="H159" s="4" t="n">
-        <v>71</v>
-      </c>
-      <c r="I159" s="4" t="inlineStr"/>
-      <c r="J159" s="4" t="inlineStr"/>
-      <c r="K159" s="4" t="inlineStr">
-        <is>
-          <t>historico</t>
-        </is>
-      </c>
+        <v>77.89</v>
+      </c>
+      <c r="I159" s="4" t="n">
+        <v>78.18000000000001</v>
+      </c>
+      <c r="J159" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K159" s="4" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
@@ -6963,22 +6979,22 @@
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>Eval 2025-04-01</t>
+          <t>Eval 2025-01-01</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>Estancias=70  rating=0.00(0 reviews)  canc_total=18.6%</t>
+          <t>Estancias=71  rating=0.00(0 reviews)  canc_total=20.2%</t>
         </is>
       </c>
       <c r="F160" s="4" t="n">
         <v>2025</v>
       </c>
       <c r="G160" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H160" s="4" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I160" s="4" t="inlineStr"/>
       <c r="J160" s="4" t="inlineStr"/>
@@ -7006,22 +7022,22 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Eval 2025-07-01</t>
+          <t>Eval 2025-04-01</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>Estancias=71  rating=0.00(0 reviews)  canc_total=20.2%</t>
+          <t>Estancias=70  rating=0.00(0 reviews)  canc_total=18.6%</t>
         </is>
       </c>
       <c r="F161" s="4" t="n">
         <v>2025</v>
       </c>
       <c r="G161" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H161" s="4" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I161" s="4" t="inlineStr"/>
       <c r="J161" s="4" t="inlineStr"/>
@@ -7049,22 +7065,22 @@
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>Eval 2025-10-01</t>
+          <t>Eval 2025-07-01</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>Estancias=76  rating=0.00(0 reviews)  canc_total=20.0%</t>
+          <t>Estancias=71  rating=0.00(0 reviews)  canc_total=20.2%</t>
         </is>
       </c>
       <c r="F162" s="4" t="n">
         <v>2025</v>
       </c>
       <c r="G162" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H162" s="4" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="I162" s="4" t="inlineStr"/>
       <c r="J162" s="4" t="inlineStr"/>
@@ -7092,22 +7108,22 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Eval 2026-01-01</t>
+          <t>Eval 2025-10-01</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>Estancias=71  rating=0.00(0 reviews)  canc_total=17.4%</t>
+          <t>Estancias=76  rating=0.00(0 reviews)  canc_total=20.0%</t>
         </is>
       </c>
       <c r="F163" s="4" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="G163" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H163" s="4" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I163" s="4" t="inlineStr"/>
       <c r="J163" s="4" t="inlineStr"/>
@@ -7135,19 +7151,19 @@
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>Eval 2026-04-01</t>
+          <t>Eval 2026-01-01</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>Estancias=71  rating=0.00(0 reviews)  canc_total=19.3%</t>
+          <t>Estancias=71  rating=0.00(0 reviews)  canc_total=17.4%</t>
         </is>
       </c>
       <c r="F164" s="4" t="n">
         <v>2026</v>
       </c>
       <c r="G164" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H164" s="4" t="n">
         <v>71</v>
@@ -7178,28 +7194,28 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Eval 2026-07-01</t>
+          <t>Eval 2026-04-01</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>Estancias=67  rating=0.00(0 reviews)  canc_total=18.3%</t>
+          <t>Estancias=71  rating=0.00(0 reviews)  canc_total=19.3%</t>
         </is>
       </c>
       <c r="F165" s="4" t="n">
         <v>2026</v>
       </c>
       <c r="G165" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H165" s="4" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="I165" s="4" t="inlineStr"/>
       <c r="J165" s="4" t="inlineStr"/>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>futuro</t>
+          <t>historico</t>
         </is>
       </c>
     </row>
@@ -7221,22 +7237,22 @@
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>Eval 2026-10-01</t>
+          <t>Eval 2026-07-01</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>Estancias=56  rating=0.00(0 reviews)  canc_total=12.5%</t>
+          <t>Estancias=69  rating=0.00(0 reviews)  canc_total=19.8%</t>
         </is>
       </c>
       <c r="F166" s="4" t="n">
         <v>2026</v>
       </c>
       <c r="G166" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H166" s="4" t="n">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I166" s="4" t="inlineStr"/>
       <c r="J166" s="4" t="inlineStr"/>
@@ -7264,22 +7280,22 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Eval 2027-01-01</t>
+          <t>Eval 2026-10-01</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>Estancias=46  rating=0.00(0 reviews)  canc_total=11.5%</t>
+          <t>Estancias=62  rating=0.00(0 reviews)  canc_total=16.2%</t>
         </is>
       </c>
       <c r="F167" s="4" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="G167" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H167" s="4" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="I167" s="4" t="inlineStr"/>
       <c r="J167" s="4" t="inlineStr"/>
@@ -7307,22 +7323,22 @@
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Eval 2027-04-01</t>
+          <t>Eval 2027-01-01</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>Estancias=32  rating=0.00(0 reviews)  canc_total=8.6%</t>
+          <t>Estancias=52  rating=0.00(0 reviews)  canc_total=16.1%</t>
         </is>
       </c>
       <c r="F168" s="4" t="n">
         <v>2027</v>
       </c>
       <c r="G168" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H168" s="4" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="I168" s="4" t="inlineStr"/>
       <c r="J168" s="4" t="inlineStr"/>
@@ -7335,7 +7351,7 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>Tests_Unitarios</t>
+          <t>Superhost</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
@@ -7350,28 +7366,30 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>T1a HMNKEKCM4M nights jun-2026</t>
+          <t>Eval 2027-04-01</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>nights=1 esperado=1</t>
+          <t>Estancias=38  rating=0.00(0 reviews)  canc_total=15.6%</t>
         </is>
       </c>
       <c r="F169" s="4" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="G169" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H169" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I169" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="I169" s="4" t="inlineStr"/>
       <c r="J169" s="4" t="inlineStr"/>
-      <c r="K169" s="4" t="inlineStr"/>
+      <c r="K169" s="4" t="inlineStr">
+        <is>
+          <t>futuro</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
@@ -7391,12 +7409,12 @@
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>T1b HMNKEKCM4M continuación jul-2026</t>
+          <t>T2a HMHM4FQMHK nights jul-2026</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>Continuación encontrada</t>
+          <t>nights=2 esperado=2</t>
         </is>
       </c>
       <c r="F170" s="4" t="n">
@@ -7405,8 +7423,12 @@
       <c r="G170" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H170" s="4" t="inlineStr"/>
-      <c r="I170" s="4" t="inlineStr"/>
+      <c r="H170" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I170" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="J170" s="4" t="inlineStr"/>
       <c r="K170" s="4" t="inlineStr"/>
     </row>
@@ -7428,19 +7450,19 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>T1c (2026,6) en distorted_months</t>
+          <t>T2b (2026,7) en distorted_months</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>(2026,6) in distorted_months = True</t>
+          <t>(2026,7) in distorted_months = True</t>
         </is>
       </c>
       <c r="F171" s="4" t="n">
         <v>2026</v>
       </c>
       <c r="G171" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H171" s="4" t="inlineStr"/>
       <c r="I171" s="4" t="inlineStr"/>
@@ -7465,25 +7487,25 @@
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>T1d PM jun-2026 formula corregida (delta&lt;5%)</t>
+          <t>T3 HMZRBPTXRS nights feb-2026</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>PM_correcto=81.24  PM_dashboard=81.24  delta=0.0%</t>
+          <t>nights=3 esperado=3 checkin=2026-02-26</t>
         </is>
       </c>
       <c r="F172" s="4" t="n">
         <v>2026</v>
       </c>
       <c r="G172" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H172" s="4" t="n">
-        <v>81.23999999999999</v>
+        <v>3</v>
       </c>
       <c r="I172" s="4" t="n">
-        <v>81.23999999999999</v>
+        <v>3</v>
       </c>
       <c r="J172" s="4" t="inlineStr"/>
       <c r="K172" s="4" t="inlineStr"/>
@@ -7506,7 +7528,7 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>T2a HMHM4FQMHK nights jul-2026</t>
+          <t>T4 Lisanne Vladisavljevic 2021-09</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
@@ -7515,10 +7537,10 @@
         </is>
       </c>
       <c r="F173" s="4" t="n">
-        <v>2026</v>
+        <v>2021</v>
       </c>
       <c r="G173" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H173" s="4" t="n">
         <v>2</v>
@@ -7547,22 +7569,26 @@
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>T2b (2026,7) en distorted_months</t>
+          <t>T5 Mireille Heronneau 2021-10</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>(2026,7) in distorted_months = True</t>
+          <t>nights=2 esperado=2</t>
         </is>
       </c>
       <c r="F174" s="4" t="n">
-        <v>2026</v>
+        <v>2021</v>
       </c>
       <c r="G174" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="H174" s="4" t="inlineStr"/>
-      <c r="I174" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="H174" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I174" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="J174" s="4" t="inlineStr"/>
       <c r="K174" s="4" t="inlineStr"/>
     </row>
@@ -7584,25 +7610,25 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>T3 HMZRBPTXRS nights feb-2026</t>
+          <t>T6 Elisabeth Liwadas Kreutz 2022-05</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>nights=3 esperado=3 checkin=2026-02-26</t>
+          <t>nights=5 esperado=5</t>
         </is>
       </c>
       <c r="F175" s="4" t="n">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="G175" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H175" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I175" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J175" s="4" t="inlineStr"/>
       <c r="K175" s="4" t="inlineStr"/>
@@ -7610,7 +7636,7 @@
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>Tests_Unitarios</t>
+          <t>Totales_Anuales</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
@@ -7625,33 +7651,33 @@
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>T4 Lisanne Vladisavljevic 2021-09</t>
+          <t>Anual 2015</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>nights=2 esperado=2</t>
+          <t>Ingresos=9051.0€  Noches=110  PM_ok=75.30  PM_dash=77.10  delta=2.4%</t>
         </is>
       </c>
       <c r="F176" s="4" t="n">
-        <v>2021</v>
-      </c>
-      <c r="G176" s="4" t="n">
-        <v>9</v>
-      </c>
+        <v>2015</v>
+      </c>
+      <c r="G176" s="4" t="inlineStr"/>
       <c r="H176" s="4" t="n">
-        <v>2</v>
+        <v>75.3</v>
       </c>
       <c r="I176" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J176" s="4" t="inlineStr"/>
+        <v>77.09999999999999</v>
+      </c>
+      <c r="J176" s="4" t="n">
+        <v>2.4</v>
+      </c>
       <c r="K176" s="4" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>Tests_Unitarios</t>
+          <t>Totales_Anuales</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
@@ -7666,33 +7692,33 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>T5 Mireille Heronneau 2021-10</t>
+          <t>Anual 2016</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>nights=2 esperado=2</t>
+          <t>Ingresos=11388.0€  Noches=173  PM_ok=64.07  PM_dash=61.55  delta=3.9%</t>
         </is>
       </c>
       <c r="F177" s="4" t="n">
-        <v>2021</v>
-      </c>
-      <c r="G177" s="4" t="n">
-        <v>10</v>
-      </c>
+        <v>2016</v>
+      </c>
+      <c r="G177" s="4" t="inlineStr"/>
       <c r="H177" s="4" t="n">
-        <v>2</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="I177" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J177" s="4" t="inlineStr"/>
+        <v>61.55</v>
+      </c>
+      <c r="J177" s="4" t="n">
+        <v>3.9</v>
+      </c>
       <c r="K177" s="4" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>Tests_Unitarios</t>
+          <t>Totales_Anuales</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
@@ -7707,27 +7733,27 @@
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>T6 Elisabeth Liwadas Kreutz 2022-05</t>
+          <t>Anual 2017</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>nights=5 esperado=5</t>
+          <t>Ingresos=13942.0€  Noches=163  PM_ok=80.61  PM_dash=77.80  delta=3.5%</t>
         </is>
       </c>
       <c r="F178" s="4" t="n">
-        <v>2022</v>
-      </c>
-      <c r="G178" s="4" t="n">
-        <v>5</v>
-      </c>
+        <v>2017</v>
+      </c>
+      <c r="G178" s="4" t="inlineStr"/>
       <c r="H178" s="4" t="n">
-        <v>5</v>
+        <v>80.61</v>
       </c>
       <c r="I178" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J178" s="4" t="inlineStr"/>
+        <v>77.8</v>
+      </c>
+      <c r="J178" s="4" t="n">
+        <v>3.5</v>
+      </c>
       <c r="K178" s="4" t="inlineStr"/>
     </row>
     <row r="179">
@@ -7748,26 +7774,26 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Anual 2015</t>
+          <t>Anual 2018</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>Ingresos=9051.0€  Noches=110  PM_ok=75.30  PM_dash=77.10  delta=2.4%</t>
+          <t>Ingresos=16641.0€  Noches=233  PM_ok=64.51  PM_dash=62.24  delta=3.5%</t>
         </is>
       </c>
       <c r="F179" s="4" t="n">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="G179" s="4" t="inlineStr"/>
       <c r="H179" s="4" t="n">
-        <v>75.3</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="I179" s="4" t="n">
-        <v>77.09999999999999</v>
+        <v>62.24</v>
       </c>
       <c r="J179" s="4" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="K179" s="4" t="inlineStr"/>
     </row>
@@ -7789,26 +7815,26 @@
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Anual 2016</t>
+          <t>Anual 2019</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>Ingresos=11388.0€  Noches=173  PM_ok=64.07  PM_dash=61.55  delta=3.9%</t>
+          <t>Ingresos=18086.0€  Noches=250  PM_ok=66.18  PM_dash=63.78  delta=3.6%</t>
         </is>
       </c>
       <c r="F180" s="4" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="G180" s="4" t="inlineStr"/>
       <c r="H180" s="4" t="n">
-        <v>64.06999999999999</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="I180" s="4" t="n">
-        <v>61.55</v>
+        <v>63.78</v>
       </c>
       <c r="J180" s="4" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="K180" s="4" t="inlineStr"/>
     </row>
@@ -7830,26 +7856,26 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Anual 2017</t>
+          <t>Anual 2021</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>Ingresos=13942.0€  Noches=163  PM_ok=80.61  PM_dash=77.80  delta=3.5%</t>
+          <t>Ingresos=14647.0€  Noches=182  PM_ok=71.07  PM_dash=72.57  delta=2.1%</t>
         </is>
       </c>
       <c r="F181" s="4" t="n">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="G181" s="4" t="inlineStr"/>
       <c r="H181" s="4" t="n">
-        <v>80.61</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="I181" s="4" t="n">
-        <v>77.8</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="J181" s="4" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="K181" s="4" t="inlineStr"/>
     </row>
@@ -7871,26 +7897,26 @@
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Anual 2018</t>
+          <t>Anual 2022</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>Ingresos=16641.0€  Noches=233  PM_ok=64.51  PM_dash=62.24  delta=3.5%</t>
+          <t>Ingresos=18264.0€  Noches=237  PM_ok=66.91  PM_dash=66.64  delta=0.4%</t>
         </is>
       </c>
       <c r="F182" s="4" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="G182" s="4" t="inlineStr"/>
       <c r="H182" s="4" t="n">
-        <v>64.51000000000001</v>
+        <v>66.91</v>
       </c>
       <c r="I182" s="4" t="n">
-        <v>62.24</v>
+        <v>66.64</v>
       </c>
       <c r="J182" s="4" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="K182" s="4" t="inlineStr"/>
     </row>
@@ -7912,27 +7938,25 @@
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>Anual 2019</t>
+          <t>Anual 2023</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>Ingresos=18086.0€  Noches=250  PM_ok=66.18  PM_dash=63.78  delta=3.6%</t>
+          <t>Ingresos=22965.0€  Noches=302  PM_ok=64.63  PM_dash=64.64  delta=0.0%</t>
         </is>
       </c>
       <c r="F183" s="4" t="n">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="G183" s="4" t="inlineStr"/>
       <c r="H183" s="4" t="n">
-        <v>66.18000000000001</v>
+        <v>64.63</v>
       </c>
       <c r="I183" s="4" t="n">
-        <v>63.78</v>
-      </c>
-      <c r="J183" s="4" t="n">
-        <v>3.6</v>
-      </c>
+        <v>64.64</v>
+      </c>
+      <c r="J183" s="4" t="inlineStr"/>
       <c r="K183" s="4" t="inlineStr"/>
     </row>
     <row r="184">
@@ -7953,26 +7977,26 @@
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>Anual 2021</t>
+          <t>Anual 2024</t>
         </is>
       </c>
       <c r="E184" s="4" t="inlineStr">
         <is>
-          <t>Ingresos=14647.0€  Noches=182  PM_ok=71.07  PM_dash=72.57  delta=2.1%</t>
+          <t>Ingresos=25071.0€  Noches=333  PM_ok=64.04  PM_dash=63.96  delta=0.1%</t>
         </is>
       </c>
       <c r="F184" s="4" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="G184" s="4" t="inlineStr"/>
       <c r="H184" s="4" t="n">
-        <v>71.06999999999999</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="I184" s="4" t="n">
-        <v>72.56999999999999</v>
+        <v>63.96</v>
       </c>
       <c r="J184" s="4" t="n">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
       <c r="K184" s="4" t="inlineStr"/>
     </row>
@@ -7994,26 +8018,26 @@
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>Anual 2022</t>
+          <t>Anual 2025</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>Ingresos=18264.0€  Noches=237  PM_ok=66.91  PM_dash=66.64  delta=0.4%</t>
+          <t>Ingresos=25790.0€  Noches=324  PM_ok=66.85  PM_dash=67.25  delta=0.6%</t>
         </is>
       </c>
       <c r="F185" s="4" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="G185" s="4" t="inlineStr"/>
       <c r="H185" s="4" t="n">
-        <v>66.91</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="I185" s="4" t="n">
-        <v>66.64</v>
+        <v>67.25</v>
       </c>
       <c r="J185" s="4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K185" s="4" t="inlineStr"/>
     </row>
@@ -8035,25 +8059,27 @@
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>Anual 2023</t>
+          <t>Anual 2026</t>
         </is>
       </c>
       <c r="E186" s="4" t="inlineStr">
         <is>
-          <t>Ingresos=22965.0€  Noches=302  PM_ok=64.63  PM_dash=64.64  delta=0.0%</t>
+          <t>Ingresos=21667.92€  Noches=258  PM_ok=72.78  PM_dash=72.92  delta=0.2%</t>
         </is>
       </c>
       <c r="F186" s="4" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="G186" s="4" t="inlineStr"/>
       <c r="H186" s="4" t="n">
-        <v>64.63</v>
+        <v>72.78</v>
       </c>
       <c r="I186" s="4" t="n">
-        <v>64.64</v>
-      </c>
-      <c r="J186" s="4" t="inlineStr"/>
+        <v>72.92</v>
+      </c>
+      <c r="J186" s="4" t="n">
+        <v>0.2</v>
+      </c>
       <c r="K186" s="4" t="inlineStr"/>
     </row>
     <row r="187">
@@ -8074,151 +8100,28 @@
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>Anual 2024</t>
+          <t>Anual 2027</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>Ingresos=25071.0€  Noches=333  PM_ok=64.04  PM_dash=63.96  delta=0.1%</t>
+          <t>Ingresos=3035.05€  Noches=27  PM_ok=107.52  PM_dash=107.74  delta=0.2%</t>
         </is>
       </c>
       <c r="F187" s="4" t="n">
-        <v>2024</v>
+        <v>2027</v>
       </c>
       <c r="G187" s="4" t="inlineStr"/>
       <c r="H187" s="4" t="n">
-        <v>64.04000000000001</v>
+        <v>107.52</v>
       </c>
       <c r="I187" s="4" t="n">
-        <v>63.96</v>
+        <v>107.74</v>
       </c>
       <c r="J187" s="4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="K187" s="4" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="4" t="inlineStr">
-        <is>
-          <t>Totales_Anuales</t>
-        </is>
-      </c>
-      <c r="B188" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="C188" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="D188" s="4" t="inlineStr">
-        <is>
-          <t>Anual 2025</t>
-        </is>
-      </c>
-      <c r="E188" s="4" t="inlineStr">
-        <is>
-          <t>Ingresos=25790.0€  Noches=324  PM_ok=66.85  PM_dash=67.25  delta=0.6%</t>
-        </is>
-      </c>
-      <c r="F188" s="4" t="n">
-        <v>2025</v>
-      </c>
-      <c r="G188" s="4" t="inlineStr"/>
-      <c r="H188" s="4" t="n">
-        <v>66.84999999999999</v>
-      </c>
-      <c r="I188" s="4" t="n">
-        <v>67.25</v>
-      </c>
-      <c r="J188" s="4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K188" s="4" t="inlineStr"/>
-    </row>
-    <row r="189">
-      <c r="A189" s="4" t="inlineStr">
-        <is>
-          <t>Totales_Anuales</t>
-        </is>
-      </c>
-      <c r="B189" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="C189" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="D189" s="4" t="inlineStr">
-        <is>
-          <t>Anual 2026</t>
-        </is>
-      </c>
-      <c r="E189" s="4" t="inlineStr">
-        <is>
-          <t>Ingresos=20954.2€  Noches=256  PM_ok=70.75  PM_dash=71.88  delta=1.6%</t>
-        </is>
-      </c>
-      <c r="F189" s="4" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G189" s="4" t="inlineStr"/>
-      <c r="H189" s="4" t="n">
-        <v>70.75</v>
-      </c>
-      <c r="I189" s="4" t="n">
-        <v>71.88</v>
-      </c>
-      <c r="J189" s="4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K189" s="4" t="inlineStr"/>
-    </row>
-    <row r="190">
-      <c r="A190" s="4" t="inlineStr">
-        <is>
-          <t>Totales_Anuales</t>
-        </is>
-      </c>
-      <c r="B190" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="C190" s="4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="D190" s="4" t="inlineStr">
-        <is>
-          <t>Anual 2027</t>
-        </is>
-      </c>
-      <c r="E190" s="4" t="inlineStr">
-        <is>
-          <t>Ingresos=63.0€  Noches=1  PM_ok=57.46  PM_dash=57.00  delta=0.8%</t>
-        </is>
-      </c>
-      <c r="F190" s="4" t="n">
-        <v>2027</v>
-      </c>
-      <c r="G190" s="4" t="inlineStr"/>
-      <c r="H190" s="4" t="n">
-        <v>57.46</v>
-      </c>
-      <c r="I190" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="J190" s="4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K190" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8383,16 +8286,16 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>54.66</v>
+        <v>55.07</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>53.37</v>
+        <v>54</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
@@ -8407,16 +8310,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>64.65000000000001</v>
+        <v>65.55</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>63.43</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
@@ -8431,15 +8334,17 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>77.34999999999999</v>
+        <v>77.89</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>77.34</v>
-      </c>
-      <c r="E5" s="4" t="inlineStr"/>
+        <v>78.18000000000001</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0.4</v>
+      </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>OK</t>
@@ -8768,17 +8673,17 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Ingresos=20954.2€  Noches=256  PM_ok=70.75  PM_dash=71.88  delta=1.6%</t>
+          <t>Ingresos=21667.92€  Noches=258  PM_ok=72.78  PM_dash=72.92  delta=0.2%</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>70.75</v>
+        <v>72.78</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>71.88</v>
+        <v>72.92</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
@@ -8792,17 +8697,17 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Ingresos=63.0€  Noches=1  PM_ok=57.46  PM_dash=57.00  delta=0.8%</t>
+          <t>Ingresos=3035.05€  Noches=27  PM_ok=107.52  PM_dash=107.74  delta=0.2%</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>57.46</v>
+        <v>107.52</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>57</v>
+        <v>107.74</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
@@ -9044,13 +8949,13 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D8" s="4" t="inlineStr"/>
       <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Estancias=67  rating=0.00(0 reviews)  canc_total=18.3%</t>
+          <t>Estancias=69  rating=0.00(0 reviews)  canc_total=19.8%</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -9071,13 +8976,13 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D9" s="4" t="inlineStr"/>
       <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Estancias=56  rating=0.00(0 reviews)  canc_total=12.5%</t>
+          <t>Estancias=62  rating=0.00(0 reviews)  canc_total=16.2%</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -9098,13 +9003,13 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D10" s="4" t="inlineStr"/>
       <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Estancias=46  rating=0.00(0 reviews)  canc_total=11.5%</t>
+          <t>Estancias=52  rating=0.00(0 reviews)  canc_total=16.1%</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -9125,13 +9030,13 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D11" s="4" t="inlineStr"/>
       <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Estancias=32  rating=0.00(0 reviews)  canc_total=8.6%</t>
+          <t>Estancias=38  rating=0.00(0 reviews)  canc_total=15.6%</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -9151,7 +9056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:E98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10775,10 +10680,10 @@
         <v>1136</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
@@ -11006,10 +10911,10 @@
         <v>880</v>
       </c>
       <c r="C90" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>0.8</v>
+        <v>0.68</v>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
@@ -11048,10 +10953,10 @@
         <v>921</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>1.19</v>
+        <v>0.98</v>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
@@ -11159,6 +11064,27 @@
         <v>0.73</v>
       </c>
       <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>CVR 2026-05</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="n">
+        <v>1273</v>
+      </c>
+      <c r="C98" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D98" s="4" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11180,13 +11106,13 @@
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="67" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11237,31 +11163,45 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>AVISO</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Sin distorsiones graves</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Ninguna reserva cross-month distorsiona un mes significativamente</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr"/>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
-      <c r="H2" s="4" t="inlineStr"/>
-      <c r="I2" s="4" t="inlineStr"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>CrossMonth 2027-06: Pablo Ruiz</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>6n en 06/2027 + 3n en 07/2027  Total reserva=1047€  Distorsión=329€ (11% del mes)  33% de las noches son del mes siguiente</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2027-06</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>2643.19</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>2972.05</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Sin distorsión, 06/2027 mostraría ~2643€ en lugar de 2972€. Los 3n restantes están en 07/2027.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11545,7 +11485,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Ningún cambio respecto al baseline del 2026-05-26.</t>
+          <t>Ningún cambio respecto al baseline del 2026-06-18.</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr"/>
@@ -11562,7 +11502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -14782,17 +14722,17 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>81.23999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>81.23999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="E111" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>CrossMonth</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
@@ -14811,10 +14751,10 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>109.28</v>
+        <v>108.44</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>109.28</v>
+        <v>108.44</v>
       </c>
       <c r="E112" s="4" t="n">
         <v>0</v>
@@ -14840,10 +14780,10 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>109.33</v>
+        <v>121.25</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>109.33</v>
+        <v>121.25</v>
       </c>
       <c r="E113" s="4" t="n">
         <v>0</v>
@@ -14970,6 +14910,35 @@
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="D118" s="4" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="E118" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>CrossMonth</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -14986,7 +14955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -17988,7 +17957,7 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>2570.71</v>
+        <v>2808.4</v>
       </c>
       <c r="D111" s="4" t="n">
         <v>28</v>
@@ -18015,16 +17984,16 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>3161.65</v>
+        <v>3411.22</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E112" s="4" t="n">
         <v>31</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>87.09999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
@@ -18042,7 +18011,7 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>2982.71</v>
+        <v>3209.17</v>
       </c>
       <c r="D113" s="4" t="n">
         <v>25</v>
@@ -18162,6 +18131,60 @@
         <v>3.2</v>
       </c>
       <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="n">
+        <v>2972.05</v>
+      </c>
+      <c r="D118" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="E118" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F118" s="4" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E119" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="F119" s="4" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G119" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -18178,7 +18201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -18999,10 +19022,10 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>102.09</v>
+        <v>105.17</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>102.09</v>
+        <v>105.17</v>
       </c>
       <c r="E34" s="4" t="n">
         <v>0</v>
@@ -19067,19 +19090,67 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>109.62</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>109.62</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>109.73</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>109.73</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="C37" s="4" t="n">
+      <c r="C39" s="4" t="n">
         <v>57.46</v>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D39" s="4" t="n">
         <v>57.46</v>
       </c>
-      <c r="E37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="E39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -19096,7 +19167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -19182,10 +19253,10 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>519</v>
+        <v>1056</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>519</v>
+        <v>1056</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>0</v>
@@ -19209,10 +19280,10 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1159</v>
+        <v>2173</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>1159</v>
+        <v>2173</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>0</v>
@@ -19398,10 +19469,10 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1205</v>
+        <v>1682</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1205</v>
+        <v>1682</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
@@ -19425,10 +19496,10 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1577</v>
+        <v>2645</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1577</v>
+        <v>2645</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>0</v>
@@ -19749,10 +19820,10 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1689.93</v>
+        <v>2080.23</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1689.93</v>
+        <v>2080.23</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>0</v>
@@ -19803,10 +19874,10 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1697.98</v>
+        <v>2179.83</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1697.98</v>
+        <v>2179.83</v>
       </c>
       <c r="E26" s="4" t="n">
         <v>0</v>
@@ -19857,10 +19928,10 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>381.7</v>
+        <v>572.4299999999999</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>381.7</v>
+        <v>572.4299999999999</v>
       </c>
       <c r="E28" s="4" t="n">
         <v>0</v>
@@ -19992,10 +20063,10 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2308.7</v>
+        <v>3095.08</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2308.7</v>
+        <v>3095.08</v>
       </c>
       <c r="E33" s="4" t="n">
         <v>0</v>
@@ -20181,10 +20252,10 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>520.4</v>
+        <v>1718.53</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>520.4</v>
+        <v>1718.53</v>
       </c>
       <c r="E40" s="4" t="n">
         <v>0</v>
@@ -20370,10 +20441,10 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>1699.74</v>
+        <v>2303.02</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>1699.74</v>
+        <v>2303.02</v>
       </c>
       <c r="E47" s="4" t="n">
         <v>0</v>
@@ -20424,10 +20495,10 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>1211.4</v>
+        <v>1801.21</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>1211.4</v>
+        <v>1801.21</v>
       </c>
       <c r="E49" s="4" t="n">
         <v>0</v>
@@ -20443,18 +20514,18 @@
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Ene</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>194</v>
+        <v>169.69</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>194</v>
+        <v>169.69</v>
       </c>
       <c r="E50" s="4" t="n">
         <v>0</v>
@@ -20474,14 +20545,14 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Ene</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>619</v>
+        <v>194</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>619</v>
+        <v>194</v>
       </c>
       <c r="E51" s="4" t="n">
         <v>0</v>
@@ -20501,14 +20572,14 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>1630</v>
+        <v>619</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>1630</v>
+        <v>619</v>
       </c>
       <c r="E52" s="4" t="n">
         <v>0</v>
@@ -20528,14 +20599,14 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Abr</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>1555</v>
+        <v>1630</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>1555</v>
+        <v>1630</v>
       </c>
       <c r="E53" s="4" t="n">
         <v>0</v>
@@ -20555,14 +20626,14 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Abr</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>1405</v>
+        <v>1555</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>1405</v>
+        <v>1555</v>
       </c>
       <c r="E54" s="4" t="n">
         <v>0</v>
@@ -20582,14 +20653,14 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>May</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>1375</v>
+        <v>1405</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>1375</v>
+        <v>1405</v>
       </c>
       <c r="E55" s="4" t="n">
         <v>0</v>
@@ -20609,14 +20680,14 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>2948</v>
+        <v>1681</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>2948</v>
+        <v>1681</v>
       </c>
       <c r="E56" s="4" t="n">
         <v>0</v>
@@ -20636,14 +20707,14 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Ago</t>
+          <t>Jul</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>3180</v>
+        <v>2948</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>3180</v>
+        <v>2948</v>
       </c>
       <c r="E57" s="4" t="n">
         <v>0</v>
@@ -20663,14 +20734,14 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Ago</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>327</v>
+        <v>3180</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>327</v>
+        <v>3180</v>
       </c>
       <c r="E58" s="4" t="n">
         <v>0</v>
@@ -20686,18 +20757,18 @@
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Ene</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>1139.67</v>
+        <v>327</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>1139.67</v>
+        <v>327</v>
       </c>
       <c r="E59" s="4" t="n">
         <v>0</v>
@@ -20717,14 +20788,14 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Ene</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>1181.57</v>
+        <v>1139.67</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>1181.57</v>
+        <v>1139.67</v>
       </c>
       <c r="E60" s="4" t="n">
         <v>0</v>
@@ -20744,14 +20815,14 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>1515.43</v>
+        <v>1181.57</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>1515.43</v>
+        <v>1181.57</v>
       </c>
       <c r="E61" s="4" t="n">
         <v>0</v>
@@ -20771,14 +20842,14 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Abr</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>1540</v>
+        <v>1515.43</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>1540</v>
+        <v>1515.43</v>
       </c>
       <c r="E62" s="4" t="n">
         <v>0</v>
@@ -20798,14 +20869,14 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Abr</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>1556</v>
+        <v>1540</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>1556</v>
+        <v>1540</v>
       </c>
       <c r="E63" s="4" t="n">
         <v>0</v>
@@ -20825,14 +20896,14 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>May</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>2738</v>
+        <v>1556</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>2738</v>
+        <v>1556</v>
       </c>
       <c r="E64" s="4" t="n">
         <v>0</v>
@@ -20852,14 +20923,14 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>2996.17</v>
+        <v>2738</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>2996.17</v>
+        <v>2738</v>
       </c>
       <c r="E65" s="4" t="n">
         <v>0</v>
@@ -20879,14 +20950,14 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Ago</t>
+          <t>Jul</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>2741.63</v>
+        <v>2996.17</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>2741.63</v>
+        <v>2996.17</v>
       </c>
       <c r="E66" s="4" t="n">
         <v>0</v>
@@ -20906,14 +20977,14 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Ago</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>2010.96</v>
+        <v>2741.63</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>2010.96</v>
+        <v>2741.63</v>
       </c>
       <c r="E67" s="4" t="n">
         <v>0</v>
@@ -20933,14 +21004,14 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>221.57</v>
+        <v>2526.96</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>221.57</v>
+        <v>2526.96</v>
       </c>
       <c r="E68" s="4" t="n">
         <v>0</v>
@@ -20956,18 +21027,18 @@
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Ene</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>1371.44</v>
+        <v>616.5700000000001</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>1371.44</v>
+        <v>616.5700000000001</v>
       </c>
       <c r="E69" s="4" t="n">
         <v>0</v>
@@ -20987,14 +21058,14 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Ene</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>1406.68</v>
+        <v>1371.44</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>1406.68</v>
+        <v>1371.44</v>
       </c>
       <c r="E70" s="4" t="n">
         <v>0</v>
@@ -21014,14 +21085,14 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>1572.63</v>
+        <v>1406.68</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>1572.63</v>
+        <v>1406.68</v>
       </c>
       <c r="E71" s="4" t="n">
         <v>0</v>
@@ -21041,14 +21112,14 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Abr</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>1792.25</v>
+        <v>1572.63</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>1792.25</v>
+        <v>1572.63</v>
       </c>
       <c r="E72" s="4" t="n">
         <v>0</v>
@@ -21068,14 +21139,14 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Abr</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>1938</v>
+        <v>1792.25</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>1938</v>
+        <v>1792.25</v>
       </c>
       <c r="E73" s="4" t="n">
         <v>0</v>
@@ -21095,14 +21166,14 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>May</t>
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>2613</v>
+        <v>1938</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>2613</v>
+        <v>1938</v>
       </c>
       <c r="E74" s="4" t="n">
         <v>0</v>
@@ -21122,14 +21193,14 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>3162</v>
+        <v>2613</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>3162</v>
+        <v>2613</v>
       </c>
       <c r="E75" s="4" t="n">
         <v>0</v>
@@ -21149,14 +21220,14 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Ago</t>
+          <t>Jul</t>
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>2204</v>
+        <v>3392</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>2204</v>
+        <v>3392</v>
       </c>
       <c r="E76" s="4" t="n">
         <v>0</v>
@@ -21176,14 +21247,14 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Ago</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>2194</v>
+        <v>2204</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>2194</v>
+        <v>2204</v>
       </c>
       <c r="E77" s="4" t="n">
         <v>0</v>
@@ -21203,14 +21274,14 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>283</v>
+        <v>2194</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>283</v>
+        <v>2194</v>
       </c>
       <c r="E78" s="4" t="n">
         <v>0</v>
@@ -21226,18 +21297,18 @@
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Ene</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>1228</v>
+        <v>283</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>1228</v>
+        <v>283</v>
       </c>
       <c r="E79" s="4" t="n">
         <v>0</v>
@@ -21257,14 +21328,14 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Ene</t>
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>1270</v>
+        <v>1228</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>1270</v>
+        <v>1228</v>
       </c>
       <c r="E80" s="4" t="n">
         <v>0</v>
@@ -21284,14 +21355,14 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>1635.67</v>
+        <v>1270</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>1635.67</v>
+        <v>1270</v>
       </c>
       <c r="E81" s="4" t="n">
         <v>0</v>
@@ -21311,14 +21382,14 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Abr</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>2048.33</v>
+        <v>1635.67</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>2048.33</v>
+        <v>1635.67</v>
       </c>
       <c r="E82" s="4" t="n">
         <v>0</v>
@@ -21338,14 +21409,14 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Abr</t>
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>2097</v>
+        <v>2048.33</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>2097</v>
+        <v>2048.33</v>
       </c>
       <c r="E83" s="4" t="n">
         <v>0</v>
@@ -21365,14 +21436,14 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>May</t>
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>2478</v>
+        <v>2097</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>2478</v>
+        <v>2097</v>
       </c>
       <c r="E84" s="4" t="n">
         <v>0</v>
@@ -21392,14 +21463,14 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>2662</v>
+        <v>2679</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>2662</v>
+        <v>2679</v>
       </c>
       <c r="E85" s="4" t="n">
         <v>0</v>
@@ -21419,14 +21490,14 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Ago</t>
+          <t>Jul</t>
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>2941</v>
+        <v>2662</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>2941</v>
+        <v>2662</v>
       </c>
       <c r="E86" s="4" t="n">
         <v>0</v>
@@ -21446,14 +21517,14 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Ago</t>
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>2842.83</v>
+        <v>3093</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>2842.83</v>
+        <v>3093</v>
       </c>
       <c r="E87" s="4" t="n">
         <v>0</v>
@@ -21473,14 +21544,14 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>1963.17</v>
+        <v>2842.83</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>1963.17</v>
+        <v>2842.83</v>
       </c>
       <c r="E88" s="4" t="n">
         <v>0</v>
@@ -21496,18 +21567,18 @@
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Ene</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>1134.29</v>
+        <v>1963.17</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>1134.29</v>
+        <v>1963.17</v>
       </c>
       <c r="E89" s="4" t="n">
         <v>0</v>
@@ -21527,14 +21598,14 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Ene</t>
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>1220.77</v>
+        <v>1134.29</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>1220.77</v>
+        <v>1134.29</v>
       </c>
       <c r="E90" s="4" t="n">
         <v>0</v>
@@ -21554,14 +21625,14 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>1419.72</v>
+        <v>1220.77</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>1419.72</v>
+        <v>1220.77</v>
       </c>
       <c r="E91" s="4" t="n">
         <v>0</v>
@@ -21581,14 +21652,14 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Abr</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>1731.09</v>
+        <v>1419.72</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>1731.09</v>
+        <v>1419.72</v>
       </c>
       <c r="E92" s="4" t="n">
         <v>0</v>
@@ -21608,14 +21679,14 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Abr</t>
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>1939.39</v>
+        <v>1731.09</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>1939.39</v>
+        <v>1731.09</v>
       </c>
       <c r="E93" s="4" t="n">
         <v>0</v>
@@ -21635,14 +21706,14 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>May</t>
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>2570.71</v>
+        <v>1939.39</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>2570.71</v>
+        <v>1939.39</v>
       </c>
       <c r="E94" s="4" t="n">
         <v>0</v>
@@ -21662,14 +21733,14 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>3161.65</v>
+        <v>2808.4</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>3161.65</v>
+        <v>2808.4</v>
       </c>
       <c r="E95" s="4" t="n">
         <v>0</v>
@@ -21689,14 +21760,14 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Ago</t>
+          <t>Jul</t>
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>2982.71</v>
+        <v>3411.22</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>2982.71</v>
+        <v>3411.22</v>
       </c>
       <c r="E96" s="4" t="n">
         <v>0</v>
@@ -21716,14 +21787,14 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Ago</t>
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>3063.28</v>
+        <v>3209.17</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>3063.28</v>
+        <v>3209.17</v>
       </c>
       <c r="E97" s="4" t="n">
         <v>0</v>
@@ -21743,14 +21814,14 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>1159.09</v>
+        <v>3063.28</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>1159.09</v>
+        <v>3063.28</v>
       </c>
       <c r="E98" s="4" t="n">
         <v>0</v>
@@ -21770,14 +21841,14 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Dic</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>571.5</v>
+        <v>1159.09</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>571.5</v>
+        <v>1159.09</v>
       </c>
       <c r="E99" s="4" t="n">
         <v>0</v>
@@ -21793,26 +21864,80 @@
     </row>
     <row r="100">
       <c r="A100" s="4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>Dic</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="n">
+        <v>571.5</v>
+      </c>
+      <c r="D100" s="4" t="n">
+        <v>571.5</v>
+      </c>
+      <c r="E100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="n">
         <v>2027</v>
       </c>
-      <c r="B100" s="4" t="inlineStr">
+      <c r="B101" s="4" t="inlineStr">
         <is>
           <t>Ene</t>
         </is>
       </c>
-      <c r="C100" s="4" t="n">
+      <c r="C101" s="4" t="n">
         <v>63</v>
       </c>
-      <c r="D100" s="4" t="n">
+      <c r="D101" s="4" t="n">
         <v>63</v>
       </c>
-      <c r="E100" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" s="4" t="inlineStr">
+      <c r="E101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="n">
+        <v>2972.05</v>
+      </c>
+      <c r="D102" s="4" t="n">
+        <v>2972.05</v>
+      </c>
+      <c r="E102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -22360,12 +22485,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="51" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -22405,19 +22530,19 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>T1a HMNKEKCM4M nights jun-2026</t>
+          <t>T2a HMHM4FQMHK nights jul-2026</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>nights=1 esperado=1</t>
+          <t>nights=2 esperado=2</t>
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -22428,12 +22553,12 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>T1b HMNKEKCM4M continuación jul-2026</t>
+          <t>T2b (2026,7) en distorted_months</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Continuación encontrada</t>
+          <t>(2026,7) in distorted_months = True</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr"/>
@@ -22447,16 +22572,20 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>T1c (2026,6) en distorted_months</t>
+          <t>T3 HMZRBPTXRS nights feb-2026</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>(2026,6) in distorted_months = True</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
+          <t>nights=3 esperado=3 checkin=2026-02-26</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -22466,19 +22595,19 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>T1d PM jun-2026 formula corregida (delta&lt;5%)</t>
+          <t>T4 Lisanne Vladisavljevic 2021-09</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>PM_correcto=81.24  PM_dashboard=81.24  delta=0.0%</t>
+          <t>nights=2 esperado=2</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>81.23999999999999</v>
+        <v>2</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>81.23999999999999</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -22489,7 +22618,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>T2a HMHM4FQMHK nights jul-2026</t>
+          <t>T5 Mireille Heronneau 2021-10</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -22512,106 +22641,18 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>T2b (2026,7) en distorted_months</t>
+          <t>T6 Elisabeth Liwadas Kreutz 2022-05</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>(2026,7) in distorted_months = True</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>T3 HMZRBPTXRS nights feb-2026</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>nights=3 esperado=3 checkin=2026-02-26</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>T4 Lisanne Vladisavljevic 2021-09</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>nights=2 esperado=2</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>T5 Mireille Heronneau 2021-10</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>nights=2 esperado=2</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>T6 Elisabeth Liwadas Kreutz 2022-05</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
           <t>nights=5 esperado=5</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D7" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E7" s="4" t="n">
         <v>5</v>
       </c>
     </row>
